--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Mappa progetto-cliente" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Filiali diverse" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Stessa filiale" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Flussi filiali" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sintesi" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Province cantieri" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Province clienti" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mappa progetto-cliente" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filiali diverse" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stessa filiale" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flussi filiali" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sintesi" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Province cantieri" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Province clienti" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,107 +435,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tipo account</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Progetto</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Comune cantiere</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Area cantiere</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Potenza MWp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probabilità</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Stato progetto</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Fase attuale</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Indirizzo sede</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Comune sede</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>CAP sede</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Esito filiale</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Tipo match</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Score match</t>
         </is>
@@ -936,7 +948,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1037,7 +1049,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ECO GREEN SRL</t>
+          <t>ECOGREEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,7 +1140,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -1138,7 +1150,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12454,107 +12466,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tipo account</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Progetto</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Comune cantiere</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Area cantiere</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Potenza MWp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probabilità</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Stato progetto</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Fase attuale</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Indirizzo sede</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Comune sede</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>CAP sede</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Esito filiale</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Tipo match</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Score match</t>
         </is>
@@ -22469,107 +22481,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tipo account</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Progetto</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Comune cantiere</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Area cantiere</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Potenza MWp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probabilità</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Stato progetto</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Fase attuale</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Indirizzo sede</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Comune sede</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>CAP sede</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Esito filiale</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Tipo match</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Score match</t>
         </is>
@@ -22578,7 +22590,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -22679,7 +22691,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ECO GREEN SRL</t>
+          <t>ECOGREEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -22770,7 +22782,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -22780,7 +22792,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -24606,27 +24618,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>N. progetti</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MWp</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clienti unici</t>
         </is>
@@ -25991,12 +26003,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Voce</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Valore</t>
         </is>
@@ -26057,27 +26069,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>N. progetti</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MWp</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clienti unici</t>
         </is>
@@ -27043,22 +27055,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Clienti</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Progetti</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MWp</t>
         </is>

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mappa progetto-cliente" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filiali diverse" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stessa filiale" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flussi filiali" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sintesi" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Province cantieri" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Province clienti" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Mappa progetto-cliente" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Filiali diverse" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stessa filiale" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Flussi filiali" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sintesi" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Province cantieri" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Province clienti" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,107 +423,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tipo account</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Progetto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Comune cantiere</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Area cantiere</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Potenza MWp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Probabilità</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Stato progetto</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Fase attuale</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Indirizzo sede</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Comune sede</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CAP sede</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Esito filiale</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Tipo match</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Score match</t>
         </is>
@@ -948,7 +936,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1049,7 +1037,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ECOGREEN</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1140,7 +1128,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -1150,7 +1138,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12466,107 +12454,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tipo account</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Progetto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Comune cantiere</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Area cantiere</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Potenza MWp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Probabilità</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Stato progetto</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Fase attuale</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Indirizzo sede</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Comune sede</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CAP sede</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Esito filiale</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Tipo match</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Score match</t>
         </is>
@@ -22481,107 +22469,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tipo account</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Progetto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Comune cantiere</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Area cantiere</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Potenza MWp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Probabilità</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Stato progetto</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Fase attuale</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Indirizzo sede</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Comune sede</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CAP sede</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Esito filiale</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Tipo match</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Score match</t>
         </is>
@@ -22590,7 +22578,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -22691,7 +22679,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ECOGREEN</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -22782,7 +22770,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -22792,7 +22780,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -24618,27 +24606,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>N. progetti</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MWp</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clienti unici</t>
         </is>
@@ -26003,12 +25991,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Voce</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Valore</t>
         </is>
@@ -26069,27 +26057,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>N. progetti</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MWp</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clienti unici</t>
         </is>
@@ -27055,22 +27043,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Clienti</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Progetti</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MWp</t>
         </is>

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mappa progetto-cliente" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filiali diverse" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stessa filiale" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flussi filiali" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sintesi" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Province cantieri" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Province clienti" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Mappa progetto-cliente" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Filiali diverse" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stessa filiale" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Flussi filiali" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sintesi" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Province cantieri" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Province clienti" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,111 +419,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U119"/>
+  <dimension ref="A1:U121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tipo account</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Progetto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Comune cantiere</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Area cantiere</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Potenza MWp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Probabilità</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Stato progetto</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Fase attuale</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Indirizzo sede</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Comune sede</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CAP sede</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Esito filiale</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Tipo match</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Score match</t>
         </is>
@@ -948,7 +936,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1049,7 +1037,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ECOGREEN</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1140,7 +1128,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -1150,7 +1138,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8220,12 +8208,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8235,7 +8223,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Aree Sud</t>
+          <t>ISILI 2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8245,12 +8233,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Sud Sardegna</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porto Torres</t>
+          <t>Isili</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8260,11 +8248,11 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>50.6</v>
+        <v>33.527</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -8281,32 +8269,32 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>VIA GIUSEPPE RIPAMONTI 85</t>
+          <t>VIA ALGHERO 33</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CAGLIARI</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8321,12 +8309,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8336,7 +8324,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>F-Sassa</t>
+          <t>Aree Sud</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8351,21 +8339,21 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
+          <t>Porto Torres</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
           <t>Sassari</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Sassari</t>
-        </is>
-      </c>
       <c r="J79" t="n">
-        <v>30.15</v>
+        <v>50.6</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -8382,27 +8370,27 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>CORSO VITTORIO EMANUELE II 6</t>
+          <t>VIA GIUSEPPE RIPAMONTI 85</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8422,12 +8410,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8437,22 +8425,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Quistella</t>
+          <t>F-Sassa</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8462,11 +8450,11 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>56.54</v>
+        <v>30.15</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -8483,27 +8471,27 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>VIA VITTORIA NENNI 8/1</t>
+          <t>CORSO VITTORIO EMANUELE II 6</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>ALBINEA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>42020</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -8523,12 +8511,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8538,7 +8526,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Magarotto-Marconi</t>
+          <t>Quistella</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8553,7 +8541,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carpi</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8567,7 +8555,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>47.47</v>
+        <v>56.54</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -8584,27 +8572,27 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>CORSO BUENOS AIRES 54</t>
+          <t>VIA VITTORIA NENNI 8/1</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ALBINEA</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>42020</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -8624,12 +8612,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8639,22 +8627,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Blusolar Chiaravalle</t>
+          <t>Magarotto-Marconi</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chiaravalle</t>
+          <t>Carpi</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8664,11 +8652,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>38.16</v>
+        <v>47.47</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -8685,27 +8673,27 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>VIA CARAVAGGIO 125</t>
+          <t>CORSO BUENOS AIRES 54</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>PESCARA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>65125</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -8725,12 +8713,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8740,22 +8728,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Greppo</t>
+          <t>Blusolar Chiaravalle</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Montepulciano</t>
+          <t>Chiaravalle</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8765,11 +8753,11 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>26.6</v>
+        <v>38.16</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -8786,27 +8774,27 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>VIALE DELL'ARTE 25</t>
+          <t>VIA CARAVAGGIO 125</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PESCARA</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>65125</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -8826,12 +8814,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8841,36 +8829,36 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Olivola</t>
+          <t>FOSSATONE</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Massa Lombarda</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>77.98999999999999</v>
+        <v>61.271</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -8887,27 +8875,27 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>VIA ANDREA DORIA 41 G</t>
+          <t>VIA PIETRO NENNI 6/E</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -8927,12 +8915,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -8942,36 +8930,36 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Greppo</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Montepulciano</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>18.58</v>
+        <v>26.6</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -8988,27 +8976,27 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIALE DELL'ARTE 25</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9028,12 +9016,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9043,7 +9031,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PV Ambrosi</t>
+          <t>Olivola</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9058,7 +9046,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Amorosi</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9072,7 +9060,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>28.3</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -9089,28 +9077,32 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>CENTRO DIREZIONALE SNC</t>
+          <t>VIA ANDREA DORIA 41 G</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>80143</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr"/>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -9125,12 +9117,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9140,7 +9132,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Francavilla</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9150,12 +9142,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9169,7 +9161,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>48.48</v>
+        <v>18.58</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -9186,27 +9178,27 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>VIA DEL LAURO 9</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9226,12 +9218,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9241,7 +9233,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cancello ed Arnone 2</t>
+          <t>PV Ambrosi</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9251,12 +9243,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Amorosi</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9270,7 +9262,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>33.74</v>
+        <v>28.3</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -9287,32 +9279,28 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>CENTRO DIREZIONALE SNC</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>40125</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
+          <t>80143</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -9327,12 +9315,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9342,7 +9330,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>C_023</t>
+          <t>Francavilla</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9352,12 +9340,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sessa Aurunca</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9371,7 +9359,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>19.021</v>
+        <v>48.48</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -9388,27 +9376,27 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>VIA JULIUS DURST 6</t>
+          <t>VIA DEL LAURO 9</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>BRESSANONE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>39042</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9443,7 +9431,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CASTEL VOLTURNO 2</t>
+          <t>Cancello ed Arnone 2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9472,7 +9460,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>55.26</v>
+        <v>33.74</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -9529,12 +9517,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9544,7 +9532,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>FV GRAZZANISE</t>
+          <t>C_023</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9559,7 +9547,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Grazzanise</t>
+          <t>Sessa Aurunca</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9573,7 +9561,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>21.5</v>
+        <v>19.021</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -9590,27 +9578,27 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>GALLERIA DE CRISTOFORIS 1</t>
+          <t>VIA JULIUS DURST 6</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BRESSANONE</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -9630,12 +9618,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9645,36 +9633,36 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Maag Black Sheep</t>
+          <t>CASTEL VOLTURNO 2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>11.45</v>
+        <v>55.26</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -9691,23 +9679,27 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>VIA FRANCESCO CRISPI 98</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>80121</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr"/>
+          <t>40125</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -9727,12 +9719,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9742,36 +9734,36 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PV Piegaro</t>
+          <t>FV GRAZZANISE</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Piegaro</t>
+          <t>Grazzanise</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>9.199999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -9788,27 +9780,27 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>VIA ROMA 151</t>
+          <t>GALLERIA DE CRISTOFORIS 1</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>BORGO CHIESE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>38083</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -9828,12 +9820,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -9843,7 +9835,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Agrivoltaico Orvieto</t>
+          <t>Maag Black Sheep</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9858,7 +9850,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Orvieto</t>
+          <t>Castel Giorgio</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9872,7 +9864,7 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>33.972</v>
+        <v>11.45</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -9889,27 +9881,23 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>VIA GERMANICO 101</t>
+          <t>VIA FRANCESCO CRISPI 98</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>RM</t>
-        </is>
-      </c>
+          <t>80121</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -9929,12 +9917,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9944,7 +9932,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Città della Pieve - Agricola Pievese</t>
+          <t>PV Piegaro</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9959,7 +9947,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Città della Pieve</t>
+          <t>Piegaro</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9973,7 +9961,7 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>34.776</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -9990,27 +9978,27 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
+          <t>VIA ROMA 151</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>BORGO CHIESE</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10030,12 +10018,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10045,7 +10033,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AV1 - Castiglione del Lago Morami</t>
+          <t>Agrivoltaico Orvieto</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10055,26 +10043,26 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Orvieto</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Castiglione del Lago</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J96" t="n">
-        <v>16.974</v>
+        <v>33.972</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -10091,27 +10079,27 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 7</t>
+          <t>VIA GERMANICO 101</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10131,12 +10119,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10146,7 +10134,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>PV Castel San Giorgio</t>
+          <t>Città della Pieve - Agricola Pievese</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10156,12 +10144,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Città della Pieve</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10175,7 +10163,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>34.6</v>
+        <v>34.776</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -10192,27 +10180,27 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10232,12 +10220,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10247,7 +10235,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Contrada Fagiolo</t>
+          <t>AV1 - Castiglione del Lago Morami</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10257,12 +10245,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Castiglione del Lago</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10276,7 +10264,7 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>55.55</v>
+        <v>16.974</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -10293,7 +10281,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>VIA GALILEO GALILEI 7</t>
+          <t>VIA BERGAMO 7</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -10303,7 +10291,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -10313,7 +10301,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10333,12 +10321,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -10348,36 +10336,36 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Casalone</t>
+          <t>PV Castel San Giorgio</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Terni</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Castel Giorgio</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>36.3</v>
+        <v>34.6</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -10394,7 +10382,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>VIA AGNELLO 18</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -10404,7 +10392,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -10434,12 +10422,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10449,36 +10437,36 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Rieti-1</t>
+          <t>Contrada Fagiolo</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Terni</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Castel Giorgio</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>7</v>
+        <v>55.55</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -10495,7 +10483,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>VIA GABRIO SERBELLONI 5</t>
+          <t>VIA GALILEO GALILEI 7</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -10505,7 +10493,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -10515,7 +10503,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -10535,12 +10523,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10550,7 +10538,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Rieti-2</t>
+          <t>Casalone</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10560,12 +10548,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -10579,7 +10567,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>10</v>
+        <v>36.3</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -10596,7 +10584,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>VIA GABRIO SERBELLONI 5</t>
+          <t>VIA AGNELLO 18</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10606,7 +10594,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -10636,12 +10624,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -10651,36 +10639,36 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PV Ferrara</t>
+          <t>Rieti-1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>31.4</v>
+        <v>7</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -10697,27 +10685,27 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>VICOLO DEI GABBIANI 30</t>
+          <t>VIA GABRIO SERBELLONI 5</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -10737,93 +10725,93 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Energy Park Faenza</t>
+          <t>Rieti-2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Faenza</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Completato</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>VIA II GIUGNO 1-3</t>
+          <t>VIA GABRIO SERBELLONI 5</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>DOZZA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -10838,22 +10826,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PV Bologna 1</t>
+          <t>PV Ferrara</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10863,68 +10851,68 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="J104" t="n">
-        <v>6</v>
+        <v>31.4</v>
       </c>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE SELICE 55/A</t>
+          <t>VICOLO DEI GABBIANI 30</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -10939,22 +10927,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VIGARANO MAINARDA</t>
+          <t>Energy Park Faenza</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10964,12 +10952,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Vigarano Mainarda</t>
+          <t>Faenza</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10983,49 +10971,49 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>26.1</v>
+        <v>14</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Completato</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>VIA BERNINA 7</t>
+          <t>VIA II GIUGNO 1-3</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>DOZZA</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11040,22 +11028,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PV Codigoro</t>
+          <t>PV Bologna 1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -11065,12 +11053,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Codigoro</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11084,49 +11072,49 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>24.95</v>
+        <v>6</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
+          <t>VIA PROVINCIALE SELICE 55/A</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -11141,12 +11129,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -11156,36 +11144,36 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>VIGARANO MAINARDA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vigarano Mainarda</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>19.5</v>
+        <v>26.1</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -11202,27 +11190,27 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11242,12 +11230,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -11257,36 +11245,36 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>PV Codigoro</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cassano all'Ionio</t>
+          <t>Codigoro</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>63.18</v>
+        <v>24.95</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -11303,27 +11291,27 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -11343,93 +11331,93 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="K109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -11444,12 +11432,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -11459,36 +11447,36 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>67.84</v>
+        <v>63.18</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -11530,7 +11518,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -11545,93 +11533,93 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>48.5</v>
+        <v>7</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -11646,12 +11634,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -11661,36 +11649,36 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>73.7</v>
+        <v>67.84</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -11707,17 +11695,17 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -11727,12 +11715,12 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
@@ -11747,88 +11735,88 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>7</v>
+        <v>48.5</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -11863,36 +11851,36 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>72</v>
+        <v>73.7</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -11949,88 +11937,88 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>19.88</v>
+        <v>7</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12050,12 +12038,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -12065,36 +12053,36 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>19.96</v>
+        <v>72</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -12111,17 +12099,17 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -12131,7 +12119,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -12151,88 +12139,88 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J117" t="n">
-        <v>12</v>
+        <v>19.88</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -12252,12 +12240,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12267,36 +12255,36 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>46.7235</v>
+        <v>19.96</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -12313,7 +12301,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -12353,101 +12341,303 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PV Rubiasco</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Pinerolo</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>12</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Attivo</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Costruzione</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>VIA MATTATOIO 3</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>SALUZZO</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>12037</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Fattoria Solare Paradiso</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Poirino</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>46.7235</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>FORO BUONAPARTE 31</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>EGPM-FV082</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Latina</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>Pontinia</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>Sud</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="J119" t="n">
+      <c r="J121" t="n">
         <v>18.419</v>
       </c>
-      <c r="K119" t="n">
+      <c r="K121" t="n">
         <v>0</v>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t>In pipeline</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t>Autorizzazioni</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr">
+      <c r="N121" t="inlineStr">
         <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr">
+      <c r="O121" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
+      <c r="P121" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr">
+      <c r="Q121" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
+      <c r="R121" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
+      <c r="S121" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="T121" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U119" t="n">
+      <c r="U121" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12462,111 +12652,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U99"/>
+  <dimension ref="A1:U100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tipo account</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Progetto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Comune cantiere</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Area cantiere</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Potenza MWp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Probabilità</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Stato progetto</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Fase attuale</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Indirizzo sede</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Comune sede</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CAP sede</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Esito filiale</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Tipo match</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Score match</t>
         </is>
@@ -19342,12 +19532,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -19357,22 +19547,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Greppo</t>
+          <t>FOSSATONE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Montepulciano</t>
+          <t>Massa Lombarda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -19382,11 +19572,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>26.6</v>
+        <v>61.271</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -19403,27 +19593,27 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>VIALE DELL'ARTE 25</t>
+          <t>VIA PIETRO NENNI 6/E</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -19443,12 +19633,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -19458,36 +19648,36 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Olivola</t>
+          <t>Greppo</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Montepulciano</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>77.98999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -19504,7 +19694,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>VIA ANDREA DORIA 41 G</t>
+          <t>VIALE DELL'ARTE 25</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -19514,7 +19704,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -19544,12 +19734,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -19559,7 +19749,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Olivola</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -19569,12 +19759,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -19588,7 +19778,7 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>18.58</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -19605,27 +19795,27 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA ANDREA DORIA 41 G</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -19645,12 +19835,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -19660,7 +19850,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Francavilla</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -19670,12 +19860,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -19689,7 +19879,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>48.48</v>
+        <v>18.58</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -19706,27 +19896,27 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>VIA DEL LAURO 9</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -19746,12 +19936,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -19761,7 +19951,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cancello ed Arnone 2</t>
+          <t>Francavilla</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -19771,12 +19961,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -19790,7 +19980,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>33.74</v>
+        <v>48.48</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -19807,27 +19997,27 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA DEL LAURO 9</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -19847,12 +20037,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -19862,7 +20052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>C_023</t>
+          <t>Cancello ed Arnone 2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -19877,7 +20067,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sessa Aurunca</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -19891,7 +20081,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>19.021</v>
+        <v>33.74</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -19908,27 +20098,27 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>VIA JULIUS DURST 6</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>BRESSANONE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>39042</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -19948,12 +20138,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -19963,7 +20153,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CASTEL VOLTURNO 2</t>
+          <t>C_023</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -19978,7 +20168,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Sessa Aurunca</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -19992,7 +20182,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>55.26</v>
+        <v>19.021</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -20009,27 +20199,27 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA JULIUS DURST 6</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BRESSANONE</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -20049,12 +20239,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -20064,7 +20254,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FV GRAZZANISE</t>
+          <t>CASTEL VOLTURNO 2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -20079,7 +20269,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Grazzanise</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -20093,7 +20283,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>21.5</v>
+        <v>55.26</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -20110,27 +20300,27 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>GALLERIA DE CRISTOFORIS 1</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -20150,12 +20340,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -20165,36 +20355,36 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Maag Black Sheep</t>
+          <t>FV GRAZZANISE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Grazzanise</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>11.45</v>
+        <v>21.5</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -20211,23 +20401,27 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>VIA FRANCESCO CRISPI 98</t>
+          <t>GALLERIA DE CRISTOFORIS 1</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>80121</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr"/>
+          <t>20122</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -20247,12 +20441,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -20262,7 +20456,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PV Piegaro</t>
+          <t>Maag Black Sheep</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -20272,26 +20466,26 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Castel Giorgio</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Piegaro</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J78" t="n">
-        <v>9.199999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -20308,27 +20502,23 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>VIA ROMA 151</t>
+          <t>VIA FRANCESCO CRISPI 98</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>BORGO CHIESE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>38083</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
+          <t>80121</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -20348,12 +20538,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -20363,7 +20553,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Agrivoltaico Orvieto</t>
+          <t>PV Piegaro</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -20373,12 +20563,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Orvieto</t>
+          <t>Piegaro</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -20392,7 +20582,7 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>33.972</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -20409,27 +20599,27 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>VIA GERMANICO 101</t>
+          <t>VIA ROMA 151</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BORGO CHIESE</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -20449,12 +20639,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -20464,7 +20654,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Città della Pieve - Agricola Pievese</t>
+          <t>Agrivoltaico Orvieto</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -20474,26 +20664,26 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Orvieto</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Città della Pieve</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J80" t="n">
-        <v>34.776</v>
+        <v>33.972</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -20510,27 +20700,27 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
+          <t>VIA GERMANICO 101</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -20550,12 +20740,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -20565,7 +20755,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AV1 - Castiglione del Lago Morami</t>
+          <t>Città della Pieve - Agricola Pievese</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -20580,7 +20770,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Castiglione del Lago</t>
+          <t>Città della Pieve</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -20594,7 +20784,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>16.974</v>
+        <v>34.776</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -20611,27 +20801,27 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 7</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -20651,12 +20841,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -20666,7 +20856,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PV Castel San Giorgio</t>
+          <t>AV1 - Castiglione del Lago Morami</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -20676,12 +20866,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Castiglione del Lago</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -20695,7 +20885,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>34.6</v>
+        <v>16.974</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -20712,7 +20902,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>VIA BERGAMO 7</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -20722,7 +20912,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -20732,7 +20922,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -20752,12 +20942,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -20767,7 +20957,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Contrada Fagiolo</t>
+          <t>PV Castel San Giorgio</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -20796,7 +20986,7 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>55.55</v>
+        <v>34.6</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -20813,7 +21003,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>VIA GALILEO GALILEI 7</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -20823,7 +21013,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -20833,7 +21023,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -20853,12 +21043,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -20868,36 +21058,36 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Casalone</t>
+          <t>Contrada Fagiolo</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Terni</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Castel Giorgio</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>36.3</v>
+        <v>55.55</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -20914,7 +21104,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>VIA AGNELLO 18</t>
+          <t>VIA GALILEO GALILEI 7</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -20924,7 +21114,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -20934,7 +21124,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -20954,12 +21144,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -20969,7 +21159,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Rieti-1</t>
+          <t>Casalone</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -20979,12 +21169,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -20998,7 +21188,7 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>7</v>
+        <v>36.3</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -21015,7 +21205,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>VIA GABRIO SERBELLONI 5</t>
+          <t>VIA AGNELLO 18</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -21025,7 +21215,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -21070,7 +21260,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Rieti-2</t>
+          <t>Rieti-1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -21099,7 +21289,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -21156,12 +21346,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -21171,36 +21361,36 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PV Ferrara</t>
+          <t>Rieti-2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>31.4</v>
+        <v>10</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -21217,27 +21407,27 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>VICOLO DEI GABBIANI 30</t>
+          <t>VIA GABRIO SERBELLONI 5</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -21257,12 +21447,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -21272,7 +21462,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VIGARANO MAINARDA</t>
+          <t>PV Ferrara</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -21287,7 +21477,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Vigarano Mainarda</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -21301,7 +21491,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>26.1</v>
+        <v>31.4</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -21318,27 +21508,27 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>VIA BERNINA 7</t>
+          <t>VICOLO DEI GABBIANI 30</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -21358,12 +21548,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -21373,7 +21563,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PV Codigoro</t>
+          <t>VIGARANO MAINARDA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -21388,7 +21578,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Codigoro</t>
+          <t>Vigarano Mainarda</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -21402,7 +21592,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>24.95</v>
+        <v>26.1</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -21419,27 +21609,27 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -21459,12 +21649,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -21474,36 +21664,36 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Codigoro</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Codigoro</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>19.5</v>
+        <v>24.95</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -21520,27 +21710,27 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -21560,12 +21750,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -21575,7 +21765,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -21585,26 +21775,26 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J91" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -21621,27 +21811,27 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -21661,12 +21851,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -21676,36 +21866,36 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>48.5</v>
+        <v>63.18</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -21722,17 +21912,17 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -21742,7 +21932,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -21777,7 +21967,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -21787,12 +21977,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -21806,7 +21996,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -21863,88 +22053,88 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>7</v>
+        <v>73.7</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -21964,22 +22154,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -21989,63 +22179,63 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J95" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -22065,12 +22255,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -22080,36 +22270,36 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -22126,27 +22316,27 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -22166,12 +22356,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -22181,7 +22371,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -22210,7 +22400,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -22227,27 +22417,27 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -22267,88 +22457,88 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -22368,101 +22558,202 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PV Rubiasco</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Pinerolo</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>12</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Attivo</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Costruzione</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>VIA MATTATOIO 3</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>SALUZZO</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>12037</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>REN 176 SRL</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>REN 176 SRL</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Piemonte</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Poirino</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>Nord Ovest</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="J99" t="n">
+      <c r="J100" t="n">
         <v>46.7235</v>
       </c>
-      <c r="K99" t="n">
+      <c r="K100" t="n">
         <v>0</v>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>In pipeline</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>Autorizzazioni</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>MILANO</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>20121</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U99" t="n">
+      <c r="U100" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22477,111 +22768,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tipo account</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Progetto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Comune cantiere</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Area cantiere</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Potenza MWp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Probabilità</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Stato progetto</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Fase attuale</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Indirizzo sede</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Comune sede</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CAP sede</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Esito filiale</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Tipo match</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Score match</t>
         </is>
@@ -22590,7 +22881,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -22691,7 +22982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ECOGREEN</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -22782,7 +23073,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -22792,7 +23083,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -24004,12 +24295,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -24019,36 +24310,36 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PV Ambrosi</t>
+          <t>ISILI 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Sud Sardegna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Amorosi</t>
+          <t>Isili</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>28.3</v>
+        <v>33.527</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -24065,23 +24356,27 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>CENTRO DIREZIONALE SNC</t>
+          <t>VIA ALGHERO 33</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>CAGLIARI</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>80143</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+          <t>9127</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -24101,88 +24396,84 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Energy Park Faenza</t>
+          <t>PV Ambrosi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Faenza</t>
+          <t>Amorosi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>28.3</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Completato</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>VIA II GIUGNO 1-3</t>
+          <t>CENTRO DIREZIONALE SNC</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>DOZZA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>40060</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
+          <t>80143</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -24202,12 +24493,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24217,7 +24508,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PV Bologna 1</t>
+          <t>Energy Park Faenza</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -24227,33 +24518,33 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Faenza</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>Completato</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -24263,17 +24554,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE SELICE 55/A</t>
+          <t>VIA II GIUGNO 1-3</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>DOZZA</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -24303,12 +24594,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -24318,36 +24609,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>PV Bologna 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -24364,27 +24655,27 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA PROVINCIALE SELICE 55/A</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -24404,37 +24695,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -24444,48 +24735,48 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>67.84</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -24505,12 +24796,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -24520,36 +24811,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>18.419</v>
+        <v>67.84</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24566,40 +24857,141 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>20148</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>STESSA FILIALE</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24614,31 +25006,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Filiale cantiere</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>N. progetti</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MWp</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clienti unici</t>
         </is>
@@ -25130,19 +25522,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>60.05</v>
+        <v>61.271</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -25151,19 +25543,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>56.54</v>
+        <v>60.05</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -25172,19 +25564,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>55.55</v>
+        <v>56.54</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -25193,22 +25585,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>53.3</v>
+        <v>55.55</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -25219,35 +25611,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>50.6</v>
+        <v>53.3</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>47.47</v>
+        <v>50.6</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -25256,19 +25648,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>46.7235</v>
+        <v>47.47</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -25277,19 +25669,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>43.65</v>
+        <v>46.7235</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -25298,19 +25690,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>42.3</v>
+        <v>43.65</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -25319,19 +25711,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>38.16</v>
+        <v>42.3</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -25340,19 +25732,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>35.55</v>
+        <v>38.16</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -25361,19 +25753,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>34.776</v>
+        <v>35.55</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -25382,7 +25774,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -25394,7 +25786,7 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>34.6</v>
+        <v>34.776</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -25403,7 +25795,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -25415,7 +25807,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>33.972</v>
+        <v>34.6</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -25424,19 +25816,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>31.4</v>
+        <v>33.972</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -25445,19 +25837,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>30.15</v>
+        <v>33.527</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -25466,40 +25858,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>30.148</v>
+        <v>31.4</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>28.3</v>
+        <v>30.15</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -25508,40 +25900,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>26.6</v>
+        <v>30.148</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>26.1</v>
+        <v>28.3</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -25550,19 +25942,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>24.95</v>
+        <v>26.6</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -25571,19 +25963,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>22.57</v>
+        <v>26.1</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -25592,40 +25984,40 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>24.95</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>19.96</v>
+        <v>22.57</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -25634,40 +26026,40 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>19.88</v>
+        <v>20</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>19.5</v>
+        <v>19.96</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -25676,19 +26068,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>19.021</v>
+        <v>19.88</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -25697,19 +26089,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>18.419</v>
+        <v>19.5</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -25718,19 +26110,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>16.974</v>
+        <v>19.021</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -25739,19 +26131,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>16.63</v>
+        <v>18.419</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -25760,19 +26152,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>13.56</v>
+        <v>16.974</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -25781,19 +26173,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>12</v>
+        <v>16.63</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -25802,19 +26194,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>11.45</v>
+        <v>13.56</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -25823,19 +26215,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -25844,19 +26236,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>7</v>
+        <v>11.45</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -25865,19 +26257,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -25886,19 +26278,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -25907,40 +26299,40 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0.93</v>
+        <v>6.7</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -25949,7 +26341,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -25958,33 +26350,75 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>Bergamo</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Livorno</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>Lucca</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="n">
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
         <v>0.5</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26003,12 +26437,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Voce</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Valore</t>
         </is>
@@ -26021,7 +26455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -26031,7 +26465,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5216.814499999999</v>
+        <v>5311.612499999999</v>
       </c>
     </row>
     <row r="4">
@@ -26041,7 +26475,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -26051,7 +26485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -26069,27 +26503,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Provincia cantiere</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Regione cantiere</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>N. progetti</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MWp</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clienti unici</t>
         </is>
@@ -26455,19 +26889,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Taranto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>74.417</v>
+        <v>75.271</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -26476,40 +26910,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Taranto</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>73.7</v>
+        <v>74.417</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>73.7</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -26518,19 +26952,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Caltanissetta</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>70.23999999999999</v>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -26539,19 +26973,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Caltanissetta</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>67.84</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -26560,103 +26994,103 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>65.7235</v>
+        <v>67.84</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>63.18</v>
+        <v>65.7235</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>60.95</v>
+        <v>63.18</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>60.95</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>48.5</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -26665,61 +27099,61 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sud Sardegna</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>43.65</v>
+        <v>53.515</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>39.84</v>
+        <v>48.5</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>38.16</v>
+        <v>43.65</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -26728,40 +27162,40 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>36.3</v>
+        <v>39.84</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>26.6</v>
+        <v>38.16</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -26770,19 +27204,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sud Sardegna</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>19.988</v>
+        <v>36.3</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -26791,19 +27225,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>19.5</v>
+        <v>26.6</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -26812,19 +27246,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>18.419</v>
+        <v>19.5</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -26833,7 +27267,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -26842,10 +27276,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>18.419</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -26854,19 +27288,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -27051,26 +27485,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Provincia sede</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Clienti</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Progetti</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MWp</t>
         </is>
@@ -27131,13 +27565,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>182.63</v>
+        <v>243.901</v>
       </c>
     </row>
     <row r="6">
@@ -27395,7 +27829,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -27405,13 +27839,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>31.4</v>
+        <v>33.527</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -27421,13 +27855,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>22.57</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -27437,13 +27871,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>18.419</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -27453,13 +27887,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.63</v>
+        <v>18.419</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -27469,13 +27903,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9.199999999999999</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AN</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -27485,22 +27919,38 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.93</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>LI</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11331,12 +11331,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -11346,36 +11346,36 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>CETA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Crevalcore</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>19.5</v>
+        <v>89</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -11392,27 +11392,27 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -11432,12 +11432,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11457,26 +11457,26 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J110" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -11493,27 +11493,27 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -11533,93 +11533,93 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>7</v>
+        <v>63.18</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -11634,37 +11634,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11674,48 +11674,48 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>67.84</v>
+        <v>7</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -11735,12 +11735,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -11750,36 +11750,36 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>48.5</v>
+        <v>67.84</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -11796,17 +11796,17 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -11836,12 +11836,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -11851,36 +11851,36 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>73.7</v>
+        <v>40.31</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -11897,27 +11897,27 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -11937,88 +11937,88 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>7</v>
+        <v>48.5</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12053,36 +12053,36 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>72</v>
+        <v>73.7</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -12139,12 +12139,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -12154,36 +12154,36 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J117" t="n">
-        <v>19.88</v>
+        <v>84.3</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -12200,27 +12200,27 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -12240,88 +12240,88 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>19.96</v>
+        <v>7</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -12341,88 +12341,88 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -12442,12 +12442,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -12457,36 +12457,36 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>46.7235</v>
+        <v>19.88</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -12503,27 +12503,27 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -12543,12 +12543,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -12558,22 +12558,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -12583,11 +12583,11 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>18.419</v>
+        <v>19.96</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -12604,40 +12604,444 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
+          <t>FORO BUONAPARTE 60</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>PV Rubiasco</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Pinerolo</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>12</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Attivo</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Costruzione</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>VIA MATTATOIO 3</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>SALUZZO</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>12037</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Fattoria Solare Paradiso</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Poirino</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>46.7235</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>FORO BUONAPARTE 31</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr">
+      <c r="O125" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
+      <c r="P125" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
+      <c r="Q125" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr">
+      <c r="R125" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
+      <c r="S125" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="T125" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U121" t="n">
+      <c r="U125" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12652,7 +13056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U100"/>
+  <dimension ref="A1:U104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21750,12 +22154,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -21765,36 +22169,36 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>CETA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Crevalcore</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>19.5</v>
+        <v>89</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -21811,27 +22215,27 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -21851,12 +22255,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -21866,7 +22270,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -21876,26 +22280,26 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J92" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -21912,27 +22316,27 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -21952,12 +22356,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -21967,36 +22371,36 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>48.5</v>
+        <v>63.18</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -22013,17 +22417,17 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -22033,7 +22437,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -22053,12 +22457,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -22068,36 +22472,36 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>73.7</v>
+        <v>40.31</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -22114,27 +22518,27 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -22154,88 +22558,88 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>7</v>
+        <v>48.5</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -22270,36 +22674,36 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>72</v>
+        <v>73.7</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -22356,12 +22760,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -22371,36 +22775,36 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>19.88</v>
+        <v>84.3</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -22417,27 +22821,27 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -22457,88 +22861,88 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>19.96</v>
+        <v>7</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -22558,88 +22962,88 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -22659,12 +23063,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -22674,36 +23078,36 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>46.7235</v>
+        <v>19.88</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -22720,40 +23124,444 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
+          <t>VIA TEVERE 41</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Roma Nomentana</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>La Sterpara</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Basilicata</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Potenza</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Montemilone</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Salerno</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>FORO BUONAPARTE 60</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>PV Rubiasco</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Pinerolo</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>12</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Attivo</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Costruzione</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>VIA MATTATOIO 3</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>SALUZZO</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>12037</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Fattoria Solare Paradiso</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Poirino</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>46.7235</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
           <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>MILANO</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>20121</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="R103" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="T103" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U100" t="n">
+      <c r="U103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U104" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25006,7 +25814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25249,103 +26057,103 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Milano Nord</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>107.58</v>
+        <v>115.1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>88.39</v>
+        <v>107.58</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>86.68000000000001</v>
+        <v>88.39</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>83.3</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>77.98999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -25354,40 +26162,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bergamo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>73.3</v>
+        <v>83.3</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -25396,19 +26204,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>69.97999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -25417,19 +26225,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>67.84</v>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -25438,40 +26246,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>69.97999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>65.09999999999999</v>
+        <v>67.84</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -25485,14 +26293,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>63.18</v>
+        <v>67</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -25501,19 +26309,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>61.75</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -25522,19 +26330,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>61.271</v>
+        <v>63.18</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -25543,7 +26351,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -25555,7 +26363,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>60.05</v>
+        <v>61.75</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -25564,19 +26372,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>56.54</v>
+        <v>61.271</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -25585,19 +26393,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>55.55</v>
+        <v>60.05</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -25606,40 +26414,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>53.3</v>
+        <v>56.54</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>50.6</v>
+        <v>55.55</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -25648,22 +26456,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>47.47</v>
+        <v>53.3</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -25674,14 +26482,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>46.7235</v>
+        <v>50.6</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -25690,19 +26498,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>43.65</v>
+        <v>47.47</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -25711,19 +26519,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>42.3</v>
+        <v>46.7235</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -25737,14 +26545,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>38.16</v>
+        <v>43.65</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -25753,7 +26561,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -25765,7 +26573,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>35.55</v>
+        <v>42.3</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -25774,19 +26582,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>34.776</v>
+        <v>40.31</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -25795,19 +26603,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>34.6</v>
+        <v>38.16</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -25816,19 +26624,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>33.972</v>
+        <v>35.55</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -25837,19 +26645,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>33.527</v>
+        <v>34.776</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -25858,19 +26666,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -25879,19 +26687,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>30.15</v>
+        <v>33.972</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -25900,7 +26708,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -25909,31 +26717,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>30.148</v>
+        <v>33.527</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>28.3</v>
+        <v>31.4</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -25942,19 +26750,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>26.6</v>
+        <v>30.15</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -25963,40 +26771,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>26.1</v>
+        <v>30.148</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>24.95</v>
+        <v>28.3</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -26005,19 +26813,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>22.57</v>
+        <v>26.6</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -26026,40 +26834,40 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>20</v>
+        <v>24.95</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>19.96</v>
+        <v>22.57</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -26068,19 +26876,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>19.88</v>
+        <v>20.787</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -26094,35 +26902,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>19.021</v>
+        <v>19.96</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -26131,19 +26939,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>18.419</v>
+        <v>19.88</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -26152,19 +26960,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>16.974</v>
+        <v>19.5</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -26173,19 +26981,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>16.63</v>
+        <v>19.021</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -26194,19 +27002,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>13.56</v>
+        <v>18.419</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -26215,19 +27023,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>12</v>
+        <v>16.974</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -26236,19 +27044,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>11.45</v>
+        <v>16.63</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -26257,19 +27065,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>9.199999999999999</v>
+        <v>13.56</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -26283,14 +27091,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -26299,19 +27107,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>11.45</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -26320,19 +27128,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>6.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -26341,40 +27149,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0.93</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -26383,19 +27191,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -26404,21 +27212,84 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Livorno</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Livorno</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>Bergamo</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Livorno</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>Lucca</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="n">
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
         <v>0.5</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26455,7 +27326,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
@@ -26465,7 +27336,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5311.612499999999</v>
+        <v>5546.0095</v>
       </c>
     </row>
     <row r="4">
@@ -26485,7 +27356,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -26499,7 +27370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26700,28 +27571,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>154.77</v>
+        <v>158</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -26730,10 +27601,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>148.101</v>
+        <v>154.77</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -26742,49 +27613,49 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>135.572</v>
+        <v>148.101</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Agrigento</t>
+          <t>Terni</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>133.1</v>
+        <v>135.572</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ragusa</t>
+          <t>Agrigento</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -26796,7 +27667,7 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>125.6</v>
+        <v>133.1</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -26805,19 +27676,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Ragusa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>104.01</v>
+        <v>125.6</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -26826,19 +27697,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Oristano</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>93.45999999999999</v>
+        <v>104.01</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -26847,7 +27718,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -26856,19 +27727,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>82.45</v>
+        <v>95</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Oristano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -26880,7 +27751,7 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>80.75</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -26889,7 +27760,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -26898,31 +27769,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>75.271</v>
+        <v>82.45</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Taranto</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>74.417</v>
+        <v>80.75</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -26931,61 +27802,61 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>73.7</v>
+        <v>75.271</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Taranto</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>72</v>
+        <v>74.417</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Caltanissetta</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>70.23999999999999</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -26994,19 +27865,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Caltanissetta</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>67.84</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -27015,145 +27886,145 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>65.7235</v>
+        <v>67.84</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>63.18</v>
+        <v>65.7235</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>60.95</v>
+        <v>63.18</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>60.95</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sud Sardegna</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>53.515</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Sud Sardegna</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>48.5</v>
+        <v>53.515</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>43.65</v>
+        <v>48.5</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -27162,40 +28033,40 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>39.84</v>
+        <v>43.65</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>38.16</v>
+        <v>40.31</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -27204,40 +28075,40 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>36.3</v>
+        <v>39.84</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>26.6</v>
+        <v>38.16</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -27246,19 +28117,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>19.5</v>
+        <v>36.3</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -27267,19 +28138,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>18.419</v>
+        <v>26.6</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -27288,19 +28159,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>17</v>
+        <v>20.787</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -27309,19 +28180,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>13.56</v>
+        <v>19.5</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -27330,19 +28201,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Barletta-Andria-Trani</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>13</v>
+        <v>18.419</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -27351,40 +28222,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>13.56</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -27393,19 +28264,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Barletta-Andria-Trani</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -27414,7 +28285,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -27423,31 +28294,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -27456,21 +28327,63 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Puglia</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Livorno</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Toscana</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="n">
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
         <v>0</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27517,13 +28430,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>1907.2225</v>
+        <v>2080.5225</v>
       </c>
     </row>
     <row r="3">
@@ -27533,13 +28446,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>707.7959999999999</v>
+        <v>748.106</v>
       </c>
     </row>
     <row r="4">
@@ -27577,23 +28490,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>334.3</v>
+        <v>205.887</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -27603,23 +28516,23 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>229.8</v>
+        <v>334.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>185.1</v>
+        <v>229.8</v>
       </c>
     </row>
     <row r="9">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U125"/>
+  <dimension ref="A1:U126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11432,12 +11432,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -11447,73 +11447,73 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Terre del Reno</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Terre del Reno</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>19.5</v>
+        <v>5.4</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA GOITO 4</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>VR</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -11533,12 +11533,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11558,26 +11558,26 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J111" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -11594,27 +11594,27 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -11634,93 +11634,93 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>7</v>
+        <v>63.18</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
@@ -11735,37 +11735,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -11775,48 +11775,48 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>67.84</v>
+        <v>7</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -11836,12 +11836,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -11861,12 +11861,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -11876,11 +11876,11 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>40.31</v>
+        <v>67.84</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -11897,32 +11897,32 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -11937,12 +11937,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -11952,36 +11952,36 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>48.5</v>
+        <v>40.31</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -11998,27 +11998,27 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12082,7 +12082,7 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -12139,12 +12139,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12183,7 +12183,7 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -12200,17 +12200,17 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -12240,88 +12240,88 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>7</v>
+        <v>84.3</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -12341,22 +12341,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -12366,63 +12366,63 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J119" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -12442,12 +12442,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -12457,36 +12457,36 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -12503,27 +12503,27 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -12543,12 +12543,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -12587,7 +12587,7 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -12604,27 +12604,27 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -12644,88 +12644,88 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -12745,22 +12745,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -12789,44 +12789,44 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -12846,12 +12846,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -12861,36 +12861,36 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>20.787</v>
+        <v>46.7235</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -12907,27 +12907,27 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -12947,12 +12947,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -12962,36 +12962,36 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>18.419</v>
+        <v>20.787</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -13008,40 +13008,141 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
+      <c r="O126" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr">
+      <c r="P126" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr">
+      <c r="Q126" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr">
+      <c r="R126" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
+      <c r="S126" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
+      <c r="T126" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U125" t="n">
+      <c r="U126" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13056,7 +13157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U104"/>
+  <dimension ref="A1:U105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22255,12 +22356,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -22270,73 +22371,73 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Terre del Reno</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Terre del Reno</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>19.5</v>
+        <v>5.4</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA GOITO 4</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>VR</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -22356,12 +22457,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -22371,7 +22472,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -22381,26 +22482,26 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J93" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -22417,27 +22518,27 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -22457,12 +22558,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -22472,36 +22573,36 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>40.31</v>
+        <v>63.18</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -22518,27 +22619,27 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -22558,12 +22659,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -22573,36 +22674,36 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>48.5</v>
+        <v>40.31</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -22619,27 +22720,27 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -22674,7 +22775,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -22684,12 +22785,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -22703,7 +22804,7 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -22760,12 +22861,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -22775,7 +22876,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -22790,7 +22891,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -22804,7 +22905,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -22821,17 +22922,17 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -22841,7 +22942,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -22861,88 +22962,88 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>7</v>
+        <v>84.3</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -22962,22 +23063,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -22987,63 +23088,63 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J99" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -23063,12 +23164,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -23078,36 +23179,36 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -23124,27 +23225,27 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -23164,12 +23265,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -23179,7 +23280,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -23208,7 +23309,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -23225,27 +23326,27 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -23265,88 +23366,88 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -23366,22 +23467,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -23396,7 +23497,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -23410,44 +23511,44 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -23467,12 +23568,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -23482,36 +23583,36 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>20.787</v>
+        <v>46.7235</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -23528,40 +23629,141 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
+          <t>FORO BUONAPARTE 31</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
           <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="O105" t="inlineStr">
         <is>
           <t>TORINO</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="P105" t="inlineStr">
         <is>
           <t>10153</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="R105" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="T105" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U104" t="n">
+      <c r="U105" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25814,7 +26016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27233,19 +27435,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>0.93</v>
+        <v>5.4</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -27254,19 +27456,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -27280,7 +27482,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -27290,6 +27492,27 @@
         <v>0.5</v>
       </c>
       <c r="E70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Lucca</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E71" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27326,7 +27549,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3">
@@ -27336,7 +27559,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5546.0095</v>
+        <v>5551.409500000001</v>
       </c>
     </row>
     <row r="4">
@@ -27356,7 +27579,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -27769,13 +27992,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>82.45</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -28398,7 +28621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28838,7 +29061,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AN</t>
+          <t>VR</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -28848,22 +29071,38 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.93</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>LI</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U126"/>
+  <dimension ref="A1:U127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7804,12 +7804,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7819,22 +7819,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Velletri-Lazzaria</t>
+          <t>CSPV LEVERANO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Velletri</t>
+          <t>Nardò</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7844,11 +7844,11 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>43.65</v>
+        <v>19.578</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>VIA GIORGIO PITACCO 7</t>
+          <t>VIA SAVOIA 78</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -7905,12 +7905,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7920,36 +7920,36 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Villanova Truschedu</t>
+          <t>Velletri-Lazzaria</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oristano</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Villanova Truschedu</t>
+          <t>Velletri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>10.16</v>
+        <v>43.65</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -7966,27 +7966,27 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>VIA LARGA 2</t>
+          <t>VIA GIORGIO PITACCO 7</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>177</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8006,12 +8006,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PV Nuraminis</t>
+          <t>Villanova Truschedu</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sud Sardegna</t>
+          <t>Oristano</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nuraminis</t>
+          <t>Villanova Truschedu</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>19.988</v>
+        <v>10.16</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>GALLERIA SAN BABILA 4/C</t>
+          <t>VIA LARGA 2</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="U76" t="n">
@@ -8107,12 +8107,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Giojana</t>
+          <t>PV Nuraminis</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oristano</t>
+          <t>Sud Sardegna</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Solarussa</t>
+          <t>Nuraminis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>83.3</v>
+        <v>19.988</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -8168,27 +8168,27 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>VIA CAMPAGNOLA 40</t>
+          <t>GALLERIA SAN BABILA 4/C</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>BERGAMO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="U77" t="n">
@@ -8208,12 +8208,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ISILI 2</t>
+          <t>Giojana</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8233,12 +8233,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sud Sardegna</t>
+          <t>Oristano</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Isili</t>
+          <t>Solarussa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>33.527</v>
+        <v>83.3</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -8269,32 +8269,32 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>VIA ALGHERO 33</t>
+          <t>VIA CAMPAGNOLA 40</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>CAGLIARI</t>
+          <t>BERGAMO</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8309,12 +8309,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Aree Sud</t>
+          <t>ISILI 2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Sud Sardegna</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porto Torres</t>
+          <t>Isili</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8349,11 +8349,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>50.6</v>
+        <v>33.527</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -8370,32 +8370,32 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>VIA GIUSEPPE RIPAMONTI 85</t>
+          <t>VIA ALGHERO 33</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CAGLIARI</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -8410,12 +8410,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>F-Sassa</t>
+          <t>Aree Sud</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8440,21 +8440,21 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>Porto Torres</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
           <t>Sassari</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Sassari</t>
-        </is>
-      </c>
       <c r="J80" t="n">
-        <v>30.15</v>
+        <v>50.6</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -8471,27 +8471,27 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>CORSO VITTORIO EMANUELE II 6</t>
+          <t>VIA GIUSEPPE RIPAMONTI 85</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -8511,12 +8511,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8526,22 +8526,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Quistella</t>
+          <t>F-Sassa</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8551,11 +8551,11 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>56.54</v>
+        <v>30.15</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -8572,27 +8572,27 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>VIA VITTORIA NENNI 8/1</t>
+          <t>CORSO VITTORIO EMANUELE II 6</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>ALBINEA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>42020</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -8612,12 +8612,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Magarotto-Marconi</t>
+          <t>Quistella</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carpi</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>47.47</v>
+        <v>56.54</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -8673,27 +8673,27 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>CORSO BUENOS AIRES 54</t>
+          <t>VIA VITTORIA NENNI 8/1</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ALBINEA</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>42020</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -8713,12 +8713,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8728,22 +8728,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Blusolar Chiaravalle</t>
+          <t>Magarotto-Marconi</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chiaravalle</t>
+          <t>Carpi</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8753,11 +8753,11 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>38.16</v>
+        <v>47.47</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -8774,27 +8774,27 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>VIA CARAVAGGIO 125</t>
+          <t>CORSO BUENOS AIRES 54</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>PESCARA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>65125</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -8814,12 +8814,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8829,22 +8829,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FOSSATONE</t>
+          <t>Blusolar Chiaravalle</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Massa Lombarda</t>
+          <t>Chiaravalle</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>61.271</v>
+        <v>38.16</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -8875,27 +8875,27 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>VIA PIETRO NENNI 6/E</t>
+          <t>VIA CARAVAGGIO 125</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>PESCARA</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>65125</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -8915,12 +8915,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -8930,22 +8930,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Greppo</t>
+          <t>FOSSATONE</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Montepulciano</t>
+          <t>Massa Lombarda</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8955,11 +8955,11 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>26.6</v>
+        <v>64.67400000000001</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -8976,27 +8976,27 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>VIALE DELL'ARTE 25</t>
+          <t>VIA PIETRO NENNI 6/E</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9016,12 +9016,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9031,36 +9031,36 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Olivola</t>
+          <t>Greppo</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Montepulciano</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>77.98999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>VIA ANDREA DORIA 41 G</t>
+          <t>VIALE DELL'ARTE 25</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -9117,12 +9117,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Olivola</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>18.58</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -9178,27 +9178,27 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA ANDREA DORIA 41 G</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9218,12 +9218,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PV Ambrosi</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9243,12 +9243,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Amorosi</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>28.3</v>
+        <v>18.58</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -9279,28 +9279,32 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>CENTRO DIREZIONALE SNC</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>80143</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr"/>
+          <t>40125</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -9315,12 +9319,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9330,7 +9334,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Francavilla</t>
+          <t>PV Ambrosi</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9345,7 +9349,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Amorosi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9359,7 +9363,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>48.48</v>
+        <v>28.3</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -9376,32 +9380,28 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>VIA DEL LAURO 9</t>
+          <t>CENTRO DIREZIONALE SNC</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>20121</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
+          <t>80143</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -9416,12 +9416,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cancello ed Arnone 2</t>
+          <t>Francavilla</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>33.74</v>
+        <v>48.48</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -9477,27 +9477,27 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA DEL LAURO 9</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -9517,12 +9517,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>C_023</t>
+          <t>Cancello ed Arnone 2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sessa Aurunca</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9561,7 +9561,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>19.021</v>
+        <v>33.74</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -9578,27 +9578,27 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>VIA JULIUS DURST 6</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>BRESSANONE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>39042</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -9618,12 +9618,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CASTEL VOLTURNO 2</t>
+          <t>C_023</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Sessa Aurunca</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>55.26</v>
+        <v>19.021</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -9679,27 +9679,27 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA JULIUS DURST 6</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BRESSANONE</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -9719,12 +9719,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>FV GRAZZANISE</t>
+          <t>CASTEL VOLTURNO 2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Grazzanise</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>21.5</v>
+        <v>55.26</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -9780,27 +9780,27 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>GALLERIA DE CRISTOFORIS 1</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -9820,12 +9820,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -9835,36 +9835,36 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Maag Black Sheep</t>
+          <t>FV GRAZZANISE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Grazzanise</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>11.45</v>
+        <v>21.5</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -9881,23 +9881,27 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>VIA FRANCESCO CRISPI 98</t>
+          <t>GALLERIA DE CRISTOFORIS 1</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>80121</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr"/>
+          <t>20122</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -9917,12 +9921,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9932,7 +9936,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PV Piegaro</t>
+          <t>Maag Black Sheep</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9942,26 +9946,26 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Castel Giorgio</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Piegaro</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J95" t="n">
-        <v>9.199999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -9978,27 +9982,23 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>VIA ROMA 151</t>
+          <t>VIA FRANCESCO CRISPI 98</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>BORGO CHIESE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>38083</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
+          <t>80121</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10018,12 +10018,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Agrivoltaico Orvieto</t>
+          <t>PV Piegaro</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10043,12 +10043,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Orvieto</t>
+          <t>Piegaro</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>33.972</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -10079,27 +10079,27 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>VIA GERMANICO 101</t>
+          <t>VIA ROMA 151</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BORGO CHIESE</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10119,12 +10119,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Città della Pieve - Agricola Pievese</t>
+          <t>Agrivoltaico Orvieto</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10144,26 +10144,26 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Orvieto</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Città della Pieve</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J97" t="n">
-        <v>34.776</v>
+        <v>33.972</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -10180,27 +10180,27 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
+          <t>VIA GERMANICO 101</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10220,12 +10220,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AV1 - Castiglione del Lago Morami</t>
+          <t>Città della Pieve - Agricola Pievese</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Castiglione del Lago</t>
+          <t>Città della Pieve</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>16.974</v>
+        <v>34.776</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -10281,27 +10281,27 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 7</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10321,12 +10321,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PV Castel San Giorgio</t>
+          <t>AV1 - Castiglione del Lago Morami</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Castiglione del Lago</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>34.6</v>
+        <v>16.974</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>VIA BERGAMO 7</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -10422,12 +10422,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Contrada Fagiolo</t>
+          <t>PV Castel San Giorgio</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>55.55</v>
+        <v>34.6</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>VIA GALILEO GALILEI 7</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -10523,12 +10523,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10538,36 +10538,36 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Casalone</t>
+          <t>Contrada Fagiolo</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Terni</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Castel Giorgio</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>36.3</v>
+        <v>55.55</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>VIA AGNELLO 18</t>
+          <t>VIA GALILEO GALILEI 7</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -10624,12 +10624,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Rieti-1</t>
+          <t>Casalone</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10668,7 +10668,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>7</v>
+        <v>36.3</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>VIA GABRIO SERBELLONI 5</t>
+          <t>VIA AGNELLO 18</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Rieti-2</t>
+          <t>Rieti-1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -10826,12 +10826,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10841,36 +10841,36 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PV Ferrara</t>
+          <t>Rieti-2</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>31.4</v>
+        <v>10</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -10887,27 +10887,27 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>VICOLO DEI GABBIANI 30</t>
+          <t>VIA GABRIO SERBELLONI 5</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -10927,22 +10927,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Energy Park Faenza</t>
+          <t>PV Ferrara</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Faenza</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10971,49 +10971,49 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>14</v>
+        <v>31.4</v>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Completato</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>VIA II GIUGNO 1-3</t>
+          <t>VICOLO DEI GABBIANI 30</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>DOZZA</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11028,12 +11028,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PV Bologna 1</t>
+          <t>Energy Park Faenza</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -11053,33 +11053,33 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Faenza</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="J106" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K106" t="n">
         <v>1</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>Completato</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -11089,17 +11089,17 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE SELICE 55/A</t>
+          <t>VIA II GIUGNO 1-3</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>DOZZA</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -11129,22 +11129,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VIGARANO MAINARDA</t>
+          <t>PV Bologna 1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Vigarano Mainarda</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11173,49 +11173,49 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>26.1</v>
+        <v>6</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>VIA BERNINA 7</t>
+          <t>VIA PROVINCIALE SELICE 55/A</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -11230,12 +11230,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>PV Codigoro</t>
+          <t>VIGARANO MAINARDA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Codigoro</t>
+          <t>Vigarano Mainarda</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11274,7 +11274,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>24.95</v>
+        <v>26.1</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -11291,27 +11291,27 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -11331,12 +11331,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CETA</t>
+          <t>PV Codigoro</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11356,26 +11356,26 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Codigoro</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Crevalcore</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="J109" t="n">
-        <v>89</v>
+        <v>24.95</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -11392,27 +11392,27 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>VIA BERNINA 7</t>
+          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -11432,12 +11432,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>PV Terre del Reno</t>
+          <t>CETA</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Terre del Reno</t>
+          <t>Crevalcore</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -11476,44 +11476,44 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>5.4</v>
+        <v>89</v>
       </c>
       <c r="K110" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>VIA GOITO 4</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>LEGNANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>VR</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -11533,12 +11533,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -11548,73 +11548,73 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Terre del Reno</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Terre del Reno</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>19.5</v>
+        <v>5.4</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA GOITO 4</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>VR</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -11634,12 +11634,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11659,26 +11659,26 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J112" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -11695,27 +11695,27 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -11735,93 +11735,93 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>7</v>
+        <v>63.18</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -11836,37 +11836,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -11876,48 +11876,48 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>67.84</v>
+        <v>7</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -11937,12 +11937,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11962,12 +11962,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -11977,11 +11977,11 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>40.31</v>
+        <v>67.84</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -11998,32 +11998,32 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -12038,12 +12038,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -12053,36 +12053,36 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>48.5</v>
+        <v>40.31</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -12099,27 +12099,27 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12183,7 +12183,7 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -12240,12 +12240,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12284,7 +12284,7 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -12301,17 +12301,17 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -12341,88 +12341,88 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>7</v>
+        <v>84.3</v>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -12467,63 +12467,63 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J120" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -12543,12 +12543,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -12558,36 +12558,36 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -12604,27 +12604,27 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -12644,12 +12644,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -12705,27 +12705,27 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -12745,88 +12745,88 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -12846,22 +12846,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -12890,44 +12890,44 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -12947,12 +12947,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -12962,36 +12962,36 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>20.787</v>
+        <v>46.7235</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -13008,27 +13008,27 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -13048,12 +13048,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -13063,36 +13063,36 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>18.419</v>
+        <v>20.787</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -13109,40 +13109,141 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr">
+      <c r="O127" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr">
+      <c r="P127" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr">
+      <c r="Q127" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr">
+      <c r="R127" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
+      <c r="S127" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="T127" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U126" t="n">
+      <c r="U127" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13157,7 +13258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U105"/>
+  <dimension ref="A1:U106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19128,12 +19229,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -19143,22 +19244,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Velletri-Lazzaria</t>
+          <t>CSPV LEVERANO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Velletri</t>
+          <t>Nardò</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -19168,11 +19269,11 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>43.65</v>
+        <v>19.578</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -19189,7 +19290,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>VIA GIORGIO PITACCO 7</t>
+          <t>VIA SAVOIA 78</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -19199,7 +19300,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -19229,12 +19330,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -19244,36 +19345,36 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Villanova Truschedu</t>
+          <t>Velletri-Lazzaria</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oristano</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Villanova Truschedu</t>
+          <t>Velletri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>10.16</v>
+        <v>43.65</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -19290,27 +19391,27 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>VIA LARGA 2</t>
+          <t>VIA GIORGIO PITACCO 7</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>177</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -19330,12 +19431,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -19345,7 +19446,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PV Nuraminis</t>
+          <t>Villanova Truschedu</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -19355,12 +19456,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sud Sardegna</t>
+          <t>Oristano</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nuraminis</t>
+          <t>Villanova Truschedu</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -19374,7 +19475,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>19.988</v>
+        <v>10.16</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -19391,7 +19492,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>GALLERIA SAN BABILA 4/C</t>
+          <t>VIA LARGA 2</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -19421,7 +19522,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="U62" t="n">
@@ -19431,12 +19532,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -19446,7 +19547,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Giojana</t>
+          <t>PV Nuraminis</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -19456,12 +19557,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oristano</t>
+          <t>Sud Sardegna</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Solarussa</t>
+          <t>Nuraminis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -19475,7 +19576,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>83.3</v>
+        <v>19.988</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -19492,27 +19593,27 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>VIA CAMPAGNOLA 40</t>
+          <t>GALLERIA SAN BABILA 4/C</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>BERGAMO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -19522,7 +19623,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="U63" t="n">
@@ -19532,12 +19633,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -19547,7 +19648,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Aree Sud</t>
+          <t>Giojana</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -19557,12 +19658,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Oristano</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porto Torres</t>
+          <t>Solarussa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -19572,11 +19673,11 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>50.6</v>
+        <v>83.3</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -19593,27 +19694,27 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>VIA GIUSEPPE RIPAMONTI 85</t>
+          <t>VIA CAMPAGNOLA 40</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BERGAMO</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bergamo</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -19633,12 +19734,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -19648,7 +19749,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>F-Sassa</t>
+          <t>Aree Sud</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -19663,21 +19764,21 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>Porto Torres</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>Sassari</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Sassari</t>
-        </is>
-      </c>
       <c r="J65" t="n">
-        <v>30.15</v>
+        <v>50.6</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -19694,27 +19795,27 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>CORSO VITTORIO EMANUELE II 6</t>
+          <t>VIA GIUSEPPE RIPAMONTI 85</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -19734,12 +19835,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -19749,22 +19850,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Quistella</t>
+          <t>F-Sassa</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -19774,11 +19875,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>56.54</v>
+        <v>30.15</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -19795,27 +19896,27 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>VIA VITTORIA NENNI 8/1</t>
+          <t>CORSO VITTORIO EMANUELE II 6</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>ALBINEA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>42020</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -19835,12 +19936,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -19850,7 +19951,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Magarotto-Marconi</t>
+          <t>Quistella</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -19865,7 +19966,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carpi</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19879,7 +19980,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>47.47</v>
+        <v>56.54</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -19896,27 +19997,27 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>CORSO BUENOS AIRES 54</t>
+          <t>VIA VITTORIA NENNI 8/1</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ALBINEA</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>42020</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -19936,12 +20037,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -19951,22 +20052,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Blusolar Chiaravalle</t>
+          <t>Magarotto-Marconi</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chiaravalle</t>
+          <t>Carpi</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -19976,11 +20077,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>38.16</v>
+        <v>47.47</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -19997,27 +20098,27 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>VIA CARAVAGGIO 125</t>
+          <t>CORSO BUENOS AIRES 54</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>PESCARA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>65125</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -20037,12 +20138,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -20052,22 +20153,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FOSSATONE</t>
+          <t>Blusolar Chiaravalle</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Massa Lombarda</t>
+          <t>Chiaravalle</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -20081,7 +20182,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>61.271</v>
+        <v>38.16</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -20098,27 +20199,27 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>VIA PIETRO NENNI 6/E</t>
+          <t>VIA CARAVAGGIO 125</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>PESCARA</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>65125</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -20138,12 +20239,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -20153,22 +20254,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Greppo</t>
+          <t>FOSSATONE</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Montepulciano</t>
+          <t>Massa Lombarda</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -20178,11 +20279,11 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>26.6</v>
+        <v>64.67400000000001</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -20199,27 +20300,27 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>VIALE DELL'ARTE 25</t>
+          <t>VIA PIETRO NENNI 6/E</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -20239,12 +20340,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -20254,36 +20355,36 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Olivola</t>
+          <t>Greppo</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Montepulciano</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>77.98999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -20300,7 +20401,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>VIA ANDREA DORIA 41 G</t>
+          <t>VIALE DELL'ARTE 25</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -20310,7 +20411,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -20340,12 +20441,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -20355,7 +20456,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Olivola</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -20365,12 +20466,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -20384,7 +20485,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>18.58</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -20401,27 +20502,27 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA ANDREA DORIA 41 G</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -20441,12 +20542,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -20456,7 +20557,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Francavilla</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -20466,12 +20567,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -20485,7 +20586,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>48.48</v>
+        <v>18.58</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -20502,27 +20603,27 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>VIA DEL LAURO 9</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -20542,12 +20643,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -20557,7 +20658,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cancello ed Arnone 2</t>
+          <t>Francavilla</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -20567,12 +20668,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -20586,7 +20687,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>33.74</v>
+        <v>48.48</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -20603,27 +20704,27 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA DEL LAURO 9</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -20643,12 +20744,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -20658,7 +20759,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>C_023</t>
+          <t>Cancello ed Arnone 2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -20673,7 +20774,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sessa Aurunca</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -20687,7 +20788,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>19.021</v>
+        <v>33.74</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -20704,27 +20805,27 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>VIA JULIUS DURST 6</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>BRESSANONE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>39042</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -20744,12 +20845,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -20759,7 +20860,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CASTEL VOLTURNO 2</t>
+          <t>C_023</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -20774,7 +20875,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Sessa Aurunca</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -20788,7 +20889,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>55.26</v>
+        <v>19.021</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -20805,27 +20906,27 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA JULIUS DURST 6</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BRESSANONE</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -20845,12 +20946,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -20860,7 +20961,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>FV GRAZZANISE</t>
+          <t>CASTEL VOLTURNO 2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -20875,7 +20976,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Grazzanise</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -20889,7 +20990,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>21.5</v>
+        <v>55.26</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -20906,27 +21007,27 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>GALLERIA DE CRISTOFORIS 1</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -20946,12 +21047,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -20961,36 +21062,36 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Maag Black Sheep</t>
+          <t>FV GRAZZANISE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Grazzanise</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>11.45</v>
+        <v>21.5</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -21007,23 +21108,27 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>VIA FRANCESCO CRISPI 98</t>
+          <t>GALLERIA DE CRISTOFORIS 1</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>80121</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr"/>
+          <t>20122</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -21043,12 +21148,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -21058,7 +21163,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PV Piegaro</t>
+          <t>Maag Black Sheep</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -21068,26 +21173,26 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Castel Giorgio</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Piegaro</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J79" t="n">
-        <v>9.199999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -21104,27 +21209,23 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>VIA ROMA 151</t>
+          <t>VIA FRANCESCO CRISPI 98</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>BORGO CHIESE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>38083</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
+          <t>80121</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -21144,12 +21245,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -21159,7 +21260,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Agrivoltaico Orvieto</t>
+          <t>PV Piegaro</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -21169,12 +21270,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Orvieto</t>
+          <t>Piegaro</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -21188,7 +21289,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>33.972</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -21205,27 +21306,27 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>VIA GERMANICO 101</t>
+          <t>VIA ROMA 151</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BORGO CHIESE</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -21245,12 +21346,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -21260,7 +21361,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Città della Pieve - Agricola Pievese</t>
+          <t>Agrivoltaico Orvieto</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -21270,26 +21371,26 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Orvieto</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Città della Pieve</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J81" t="n">
-        <v>34.776</v>
+        <v>33.972</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -21306,27 +21407,27 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
+          <t>VIA GERMANICO 101</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -21346,12 +21447,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -21361,7 +21462,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AV1 - Castiglione del Lago Morami</t>
+          <t>Città della Pieve - Agricola Pievese</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -21376,7 +21477,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Castiglione del Lago</t>
+          <t>Città della Pieve</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -21390,7 +21491,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>16.974</v>
+        <v>34.776</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -21407,27 +21508,27 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 7</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -21447,12 +21548,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -21462,7 +21563,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PV Castel San Giorgio</t>
+          <t>AV1 - Castiglione del Lago Morami</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -21472,12 +21573,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Castiglione del Lago</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -21491,7 +21592,7 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>34.6</v>
+        <v>16.974</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -21508,7 +21609,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>VIA BERGAMO 7</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -21518,7 +21619,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -21528,7 +21629,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -21548,12 +21649,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -21563,7 +21664,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Contrada Fagiolo</t>
+          <t>PV Castel San Giorgio</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -21592,7 +21693,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>55.55</v>
+        <v>34.6</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -21609,7 +21710,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>VIA GALILEO GALILEI 7</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -21619,7 +21720,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -21629,7 +21730,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -21649,12 +21750,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -21664,36 +21765,36 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Casalone</t>
+          <t>Contrada Fagiolo</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Terni</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Castel Giorgio</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>36.3</v>
+        <v>55.55</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -21710,7 +21811,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>VIA AGNELLO 18</t>
+          <t>VIA GALILEO GALILEI 7</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -21720,7 +21821,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -21730,7 +21831,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -21750,12 +21851,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -21765,7 +21866,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Rieti-1</t>
+          <t>Casalone</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -21775,12 +21876,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -21794,7 +21895,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>7</v>
+        <v>36.3</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -21811,7 +21912,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>VIA GABRIO SERBELLONI 5</t>
+          <t>VIA AGNELLO 18</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -21821,7 +21922,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -21866,7 +21967,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Rieti-2</t>
+          <t>Rieti-1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -21895,7 +21996,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -21952,12 +22053,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -21967,36 +22068,36 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PV Ferrara</t>
+          <t>Rieti-2</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>31.4</v>
+        <v>10</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -22013,27 +22114,27 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>VICOLO DEI GABBIANI 30</t>
+          <t>VIA GABRIO SERBELLONI 5</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -22053,12 +22154,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -22068,7 +22169,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VIGARANO MAINARDA</t>
+          <t>PV Ferrara</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -22083,7 +22184,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Vigarano Mainarda</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -22097,7 +22198,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>26.1</v>
+        <v>31.4</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -22114,27 +22215,27 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>VIA BERNINA 7</t>
+          <t>VICOLO DEI GABBIANI 30</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -22154,12 +22255,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -22169,7 +22270,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PV Codigoro</t>
+          <t>VIGARANO MAINARDA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -22184,7 +22285,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Codigoro</t>
+          <t>Vigarano Mainarda</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -22198,7 +22299,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>24.95</v>
+        <v>26.1</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -22215,27 +22316,27 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -22255,12 +22356,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -22270,7 +22371,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CETA</t>
+          <t>PV Codigoro</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -22280,26 +22381,26 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Codigoro</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Crevalcore</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="J91" t="n">
-        <v>89</v>
+        <v>24.95</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -22316,27 +22417,27 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>VIA BERNINA 7</t>
+          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -22356,12 +22457,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -22371,7 +22472,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PV Terre del Reno</t>
+          <t>CETA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -22381,12 +22482,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Terre del Reno</t>
+          <t>Crevalcore</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -22400,44 +22501,44 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>5.4</v>
+        <v>89</v>
       </c>
       <c r="K92" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>VIA GOITO 4</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>LEGNANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>VR</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -22457,12 +22558,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -22472,73 +22573,73 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Terre del Reno</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Terre del Reno</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>19.5</v>
+        <v>5.4</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA GOITO 4</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>VR</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -22558,12 +22659,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -22573,7 +22674,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -22583,26 +22684,26 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J94" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -22619,27 +22720,27 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -22659,12 +22760,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -22674,36 +22775,36 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>40.31</v>
+        <v>63.18</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -22720,27 +22821,27 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -22760,12 +22861,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -22775,36 +22876,36 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>48.5</v>
+        <v>40.31</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -22821,27 +22922,27 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -22876,7 +22977,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -22886,12 +22987,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -22905,7 +23006,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -22962,12 +23063,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -22977,7 +23078,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -22992,7 +23093,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -23006,7 +23107,7 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -23023,17 +23124,17 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -23043,7 +23144,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -23063,88 +23164,88 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>7</v>
+        <v>84.3</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -23164,22 +23265,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -23189,63 +23290,63 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J100" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -23265,12 +23366,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -23280,36 +23381,36 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -23326,27 +23427,27 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -23366,12 +23467,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -23381,7 +23482,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -23410,7 +23511,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -23427,27 +23528,27 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -23467,88 +23568,88 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -23568,22 +23669,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -23598,7 +23699,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -23612,44 +23713,44 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -23669,12 +23770,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -23684,36 +23785,36 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>20.787</v>
+        <v>46.7235</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -23730,40 +23831,141 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
+          <t>FORO BUONAPARTE 31</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
           <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>TORINO</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="P106" t="inlineStr">
         <is>
           <t>10153</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R106" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="T106" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U105" t="n">
+      <c r="U106" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26121,13 +26323,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>278.884</v>
+        <v>298.462</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -26532,19 +26734,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>63.18</v>
+        <v>64.67400000000001</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -26553,19 +26755,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>61.75</v>
+        <v>63.18</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -26574,19 +26776,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>61.271</v>
+        <v>61.75</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -27549,7 +27751,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
@@ -27559,7 +27761,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5551.409500000001</v>
+        <v>5574.3905</v>
       </c>
     </row>
     <row r="4">
@@ -27579,7 +27781,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -27710,43 +27912,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Trapani</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>225.68</v>
+        <v>244.058</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Trapani</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>224.48</v>
+        <v>225.68</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -28037,7 +28239,7 @@
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>75.271</v>
+        <v>78.67400000000001</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -28669,13 +28871,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>748.106</v>
+        <v>767.684</v>
       </c>
     </row>
     <row r="4">
@@ -28707,7 +28909,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>243.901</v>
+        <v>247.304</v>
       </c>
     </row>
     <row r="6">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U143"/>
+  <dimension ref="A1:U144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12745,12 +12745,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -12760,36 +12760,36 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Lonato del Garda</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Lonato del Garda</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>19.5</v>
+        <v>19.27</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -12806,27 +12806,27 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -12846,12 +12846,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12871,26 +12871,26 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J124" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -12907,27 +12907,27 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -12947,93 +12947,93 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>7</v>
+        <v>63.18</v>
       </c>
       <c r="K125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -13048,37 +13048,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -13088,53 +13088,53 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -13149,12 +13149,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -13189,11 +13189,11 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>67.84</v>
+        <v>7.2</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -13230,12 +13230,12 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -13250,12 +13250,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13275,12 +13275,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -13290,11 +13290,11 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>40.31</v>
+        <v>67.84</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -13311,32 +13311,32 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -13351,12 +13351,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>14.528</v>
+        <v>40.31</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -13412,32 +13412,32 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -13452,12 +13452,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -13467,36 +13467,36 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>48.5</v>
+        <v>14.528</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -13513,17 +13513,17 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -13533,12 +13533,12 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -13578,12 +13578,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -13654,12 +13654,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -13698,7 +13698,7 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -13715,17 +13715,17 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -13755,88 +13755,88 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>7</v>
+        <v>84.3</v>
       </c>
       <c r="K133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -13856,22 +13856,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -13881,63 +13881,63 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J134" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -13957,12 +13957,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -13972,36 +13972,36 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -14018,27 +14018,27 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -14058,12 +14058,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -14102,7 +14102,7 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -14119,27 +14119,27 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -14159,12 +14159,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -14220,27 +14220,27 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -14260,88 +14260,88 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
+          <t>Potenza</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Melfi</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Salerno</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>22.925</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>VIA LUIGI BUZZI 6</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>CASALE MONFERRATO</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>15033</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
           <t>Torino</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Pinerolo</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Nord Ovest</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="J138" t="n">
-        <v>12</v>
-      </c>
-      <c r="K138" t="n">
-        <v>1</v>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>Attivo</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>Costruzione</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>VIA MATTATOIO 3</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>SALUZZO</t>
-        </is>
-      </c>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>12037</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>Cuneo</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -14361,22 +14361,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -14405,44 +14405,44 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -14462,12 +14462,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -14523,27 +14523,27 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -14563,12 +14563,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -14624,27 +14624,27 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -14664,12 +14664,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -14679,36 +14679,36 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>20.787</v>
+        <v>18.774</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -14725,27 +14725,27 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -14765,12 +14765,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -14780,36 +14780,36 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J143" t="n">
-        <v>18.419</v>
+        <v>20.787</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -14826,40 +14826,141 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O143" t="inlineStr">
+      <c r="O144" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P143" t="inlineStr">
+      <c r="P144" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q143" t="inlineStr">
+      <c r="Q144" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr">
+      <c r="R144" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
+      <c r="S144" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T143" t="inlineStr">
+      <c r="T144" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U143" t="n">
+      <c r="U144" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14874,7 +14975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U118"/>
+  <dimension ref="A1:U119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25083,12 +25184,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -25098,36 +25199,36 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Lonato del Garda</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Lonato del Garda</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>19.5</v>
+        <v>19.27</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -25144,27 +25245,27 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -25184,12 +25285,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -25199,7 +25300,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -25209,26 +25310,26 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J103" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -25245,27 +25346,27 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -25285,12 +25386,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -25300,36 +25401,36 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>7.2</v>
+        <v>63.18</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -25346,7 +25447,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -25356,7 +25457,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -25366,7 +25467,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -25386,12 +25487,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -25401,7 +25502,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -25411,12 +25512,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -25426,11 +25527,11 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>40.31</v>
+        <v>7.2</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -25447,27 +25548,27 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -25487,12 +25588,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -25502,36 +25603,36 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>48.5</v>
+        <v>40.31</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -25548,27 +25649,27 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -25603,7 +25704,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25613,12 +25714,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -25632,7 +25733,7 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -25689,12 +25790,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -25704,7 +25805,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -25719,7 +25820,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -25733,7 +25834,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -25750,17 +25851,17 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -25770,7 +25871,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -25790,88 +25891,88 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>7</v>
+        <v>84.3</v>
       </c>
       <c r="K109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -25891,22 +25992,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -25916,63 +26017,63 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J110" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -25992,12 +26093,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -26007,36 +26108,36 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -26053,27 +26154,27 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -26093,12 +26194,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -26108,7 +26209,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -26137,7 +26238,7 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -26154,27 +26255,27 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -26194,12 +26295,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -26209,7 +26310,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -26224,7 +26325,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -26238,7 +26339,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -26255,27 +26356,27 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -26295,88 +26396,88 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
+          <t>Potenza</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Melfi</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Salerno</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>22.925</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>VIA LUIGI BUZZI 6</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>CASALE MONFERRATO</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>15033</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
           <t>Torino</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Pinerolo</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Nord Ovest</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>12</v>
-      </c>
-      <c r="K114" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>Attivo</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>Costruzione</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>VIA MATTATOIO 3</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>SALUZZO</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>12037</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>Cuneo</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -26396,22 +26497,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -26426,7 +26527,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -26440,44 +26541,44 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -26497,12 +26598,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -26512,7 +26613,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -26527,7 +26628,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -26541,7 +26642,7 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -26558,27 +26659,27 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -26598,12 +26699,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -26613,7 +26714,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -26628,7 +26729,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -26642,7 +26743,7 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -26659,27 +26760,27 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -26699,12 +26800,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -26714,36 +26815,36 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>20.787</v>
+        <v>18.774</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -26760,40 +26861,141 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
+          <t>VIA SENATO 28</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
           <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr">
+      <c r="O119" t="inlineStr">
         <is>
           <t>TORINO</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr">
+      <c r="P119" t="inlineStr">
         <is>
           <t>10153</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr">
+      <c r="Q119" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr">
+      <c r="R119" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
+      <c r="S119" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
+      <c r="T119" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U118" t="n">
+      <c r="U119" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29450,7 +29652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30722,19 +30924,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>19.021</v>
+        <v>19.27</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -30743,19 +30945,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>18.419</v>
+        <v>19.021</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -30764,19 +30966,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>16.974</v>
+        <v>18.419</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -30785,19 +30987,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>16.63</v>
+        <v>16.974</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -30806,19 +31008,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>14.528</v>
+        <v>16.63</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -30827,61 +31029,61 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>14</v>
+        <v>14.528</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>13.56</v>
+        <v>14</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>11.45</v>
+        <v>13.56</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -30890,7 +31092,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30902,7 +31104,7 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>9.199999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -30911,19 +31113,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -30932,19 +31134,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -30958,7 +31160,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -30974,19 +31176,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
@@ -30995,49 +31197,49 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
         <v>5.4</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -31049,7 +31251,7 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -31058,19 +31260,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0.93</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -31079,19 +31281,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="E78" t="n">
         <v>1</v>
@@ -31105,7 +31307,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -31115,6 +31317,27 @@
         <v>0.5</v>
       </c>
       <c r="E79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Lucca</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E80" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31151,7 +31374,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
@@ -31161,7 +31384,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6197.7945</v>
+        <v>6217.0645</v>
       </c>
     </row>
     <row r="4">
@@ -31181,7 +31404,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -31195,7 +31418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32068,19 +32291,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>17</v>
+        <v>19.27</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -32089,19 +32312,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>13.56</v>
+        <v>17</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -32110,19 +32333,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Barletta-Andria-Trani</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>13</v>
+        <v>13.56</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -32131,61 +32354,61 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Barletta-Andria-Trani</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
         <v>7.2</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -32194,42 +32417,63 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Livorno</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Toscana</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="n">
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
         <v>0</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32276,13 +32520,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" t="n">
-        <v>2347.3745</v>
+        <v>2366.6445</v>
       </c>
     </row>
     <row r="3">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U144"/>
+  <dimension ref="A1:U146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9622,12 +9622,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9637,22 +9637,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Blusolar Chiaravalle</t>
+          <t>PV Novi di Modena</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chiaravalle</t>
+          <t>Novi di Modena</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9662,11 +9662,11 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>38.16</v>
+        <v>24</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -9683,27 +9683,27 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>VIA CARAVAGGIO 125</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>PESCARA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>65125</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -9723,12 +9723,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9738,22 +9738,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>FOSSATONE</t>
+          <t>Blusolar Chiaravalle</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Massa Lombarda</t>
+          <t>Chiaravalle</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>64.67400000000001</v>
+        <v>38.16</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -9784,27 +9784,27 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>VIA PIETRO NENNI 6/E</t>
+          <t>VIA CARAVAGGIO 125</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>PESCARA</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>65125</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -9824,12 +9824,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -9839,22 +9839,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Greppo</t>
+          <t>FOSSATONE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Montepulciano</t>
+          <t>Massa Lombarda</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9864,11 +9864,11 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>26.6</v>
+        <v>64.67400000000001</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -9885,27 +9885,27 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>VIALE DELL'ARTE 25</t>
+          <t>VIA PIETRO NENNI 6/E</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -9925,12 +9925,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9940,36 +9940,36 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Olivola</t>
+          <t>Greppo</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Montepulciano</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>77.98999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>VIA ANDREA DORIA 41 G</t>
+          <t>VIALE DELL'ARTE 25</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -10026,12 +10026,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Olivola</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>18.58</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -10087,27 +10087,27 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA ANDREA DORIA 41 G</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10127,12 +10127,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>PV Ambrosi</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Amorosi</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>28.3</v>
+        <v>18.58</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -10188,28 +10188,32 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>CENTRO DIREZIONALE SNC</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>80143</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr"/>
+          <t>40125</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -10224,12 +10228,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10239,7 +10243,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Francavilla</t>
+          <t>PV Ambrosi</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10254,7 +10258,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Amorosi</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10268,7 +10272,7 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>48.48</v>
+        <v>28.3</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -10285,32 +10289,28 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>VIA DEL LAURO 9</t>
+          <t>CENTRO DIREZIONALE SNC</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>20121</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
+          <t>80143</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -10325,12 +10325,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cancello ed Arnone 2</t>
+          <t>Francavilla</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10369,7 +10369,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>33.74</v>
+        <v>48.48</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -10386,27 +10386,27 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA DEL LAURO 9</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -10426,12 +10426,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>C_023</t>
+          <t>Cancello ed Arnone 2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sessa Aurunca</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>19.021</v>
+        <v>33.74</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -10487,27 +10487,27 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>VIA JULIUS DURST 6</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>BRESSANONE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>39042</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -10527,12 +10527,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CASTEL VOLTURNO 2</t>
+          <t>C_023</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Sessa Aurunca</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -10571,7 +10571,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>55.26</v>
+        <v>19.021</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -10588,27 +10588,27 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA JULIUS DURST 6</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BRESSANONE</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -10628,12 +10628,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>FV GRAZZANISE</t>
+          <t>CASTEL VOLTURNO 2</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Grazzanise</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>21.5</v>
+        <v>55.26</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -10689,27 +10689,27 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>GALLERIA DE CRISTOFORIS 1</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -10729,12 +10729,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -10744,36 +10744,36 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Maag Black Sheep</t>
+          <t>FV GRAZZANISE</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Grazzanise</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>11.45</v>
+        <v>21.5</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -10790,23 +10790,27 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>VIA FRANCESCO CRISPI 98</t>
+          <t>GALLERIA DE CRISTOFORIS 1</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>80121</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr"/>
+          <t>20122</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -10826,12 +10830,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10841,7 +10845,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PV Piegaro</t>
+          <t>Maag Black Sheep</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10851,26 +10855,26 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Castel Giorgio</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Piegaro</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J104" t="n">
-        <v>9.199999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -10887,27 +10891,23 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>VIA ROMA 151</t>
+          <t>VIA FRANCESCO CRISPI 98</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>BORGO CHIESE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>38083</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
+          <t>80121</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -10927,12 +10927,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Agrivoltaico Orvieto</t>
+          <t>PV Piegaro</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Orvieto</t>
+          <t>Piegaro</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10971,7 +10971,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>33.972</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -10988,27 +10988,27 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>VIA GERMANICO 101</t>
+          <t>VIA ROMA 151</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BORGO CHIESE</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11028,12 +11028,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Città della Pieve - Agricola Pievese</t>
+          <t>Agrivoltaico Orvieto</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -11053,26 +11053,26 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Orvieto</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Città della Pieve</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J106" t="n">
-        <v>34.776</v>
+        <v>33.972</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -11089,27 +11089,27 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
+          <t>VIA GERMANICO 101</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -11129,12 +11129,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AV1 - Castiglione del Lago Morami</t>
+          <t>Città della Pieve - Agricola Pievese</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Castiglione del Lago</t>
+          <t>Città della Pieve</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11173,7 +11173,7 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>16.974</v>
+        <v>34.776</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -11190,27 +11190,27 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 7</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11230,12 +11230,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>PV Castel San Giorgio</t>
+          <t>AV1 - Castiglione del Lago Morami</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11255,12 +11255,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Castiglione del Lago</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11274,7 +11274,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>34.6</v>
+        <v>16.974</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>VIA BERGAMO 7</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -11331,12 +11331,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Contrada Fagiolo</t>
+          <t>PV Castel San Giorgio</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11375,7 +11375,7 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>55.55</v>
+        <v>34.6</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>VIA GALILEO GALILEI 7</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -11432,12 +11432,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -11447,36 +11447,36 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Casalone</t>
+          <t>Contrada Fagiolo</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Terni</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Castel Giorgio</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>36.3</v>
+        <v>55.55</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -11493,7 +11493,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>VIA AGNELLO 18</t>
+          <t>VIA GALILEO GALILEI 7</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -11533,12 +11533,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Rieti-1</t>
+          <t>Casalone</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>7</v>
+        <v>36.3</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>VIA GABRIO SERBELLONI 5</t>
+          <t>VIA AGNELLO 18</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Rieti-2</t>
+          <t>Rieti-1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -11735,12 +11735,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PV Tarquinia</t>
+          <t>Rieti-2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Montalto di Castro</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>141.56</v>
+        <v>10</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -11796,32 +11796,32 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>CONTRADA SANT'ARCANGELO 93</t>
+          <t>VIA GABRIO SERBELLONI 5</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>BELLANTE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>64020</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -11836,12 +11836,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -11851,36 +11851,36 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PV Ferrara</t>
+          <t>PV Tarquinia</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Montalto di Castro</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>31.4</v>
+        <v>141.56</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -11897,32 +11897,32 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>VICOLO DEI GABBIANI 30</t>
+          <t>CONTRADA SANT'ARCANGELO 93</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>BELLANTE</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>64020</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -11937,22 +11937,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Energy Park Faenza</t>
+          <t>PV Ferrara</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11962,12 +11962,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Faenza</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -11981,49 +11981,49 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>14</v>
+        <v>31.4</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Completato</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>VIA II GIUGNO 1-3</t>
+          <t>VICOLO DEI GABBIANI 30</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>DOZZA</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -12038,12 +12038,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>PV Bologna 1</t>
+          <t>Energy Park Faenza</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -12063,33 +12063,33 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Faenza</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="J116" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K116" t="n">
         <v>1</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>Completato</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -12099,17 +12099,17 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE SELICE 55/A</t>
+          <t>VIA II GIUGNO 1-3</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>DOZZA</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -12139,22 +12139,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VIGARANO MAINARDA</t>
+          <t>PV Bologna 1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Vigarano Mainarda</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12183,49 +12183,49 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>26.1</v>
+        <v>6</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>VIA BERNINA 7</t>
+          <t>VIA PROVINCIALE SELICE 55/A</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -12240,12 +12240,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>PV Codigoro</t>
+          <t>VIGARANO MAINARDA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Codigoro</t>
+          <t>Vigarano Mainarda</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12284,7 +12284,7 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>24.95</v>
+        <v>26.1</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -12301,27 +12301,27 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -12341,12 +12341,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>CETA</t>
+          <t>PV Codigoro</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -12366,26 +12366,26 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Codigoro</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Crevalcore</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="J119" t="n">
-        <v>89</v>
+        <v>24.95</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -12402,27 +12402,27 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>VIA BERNINA 7</t>
+          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -12442,12 +12442,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>PV Terre del Reno</t>
+          <t>CETA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Terre del Reno</t>
+          <t>Crevalcore</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -12486,44 +12486,44 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>5.4</v>
+        <v>89</v>
       </c>
       <c r="K120" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>VIA GOITO 4</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>LEGNANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>VR</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -12543,12 +12543,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Altedo</t>
+          <t>PV Terre del Reno</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -12568,63 +12568,63 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Terre del Reno</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Malalbergo</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="J121" t="n">
-        <v>51.807</v>
+        <v>5.4</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>PIAZZA FRANCESCO CRISPI 1</t>
+          <t>VIA GOITO 4</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>90139</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>VR</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -12644,12 +12644,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PV Cento</t>
+          <t>Altedo</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pieve di Cento</t>
+          <t>Malalbergo</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>2</v>
+        <v>51.807</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -12705,27 +12705,27 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>PIAZZA FRANCESCO CRISPI 1</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>90139</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -12745,12 +12745,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -12760,36 +12760,36 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>PV Lonato del Garda</t>
+          <t>PV Cento</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lonato del Garda</t>
+          <t>Pieve di Cento</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>19.27</v>
+        <v>2</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -12806,27 +12806,27 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>VIA ARRIGO BOITO 8</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -12846,12 +12846,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -12861,36 +12861,36 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>Spinazzino</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>19.5</v>
+        <v>26.95</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -12907,27 +12907,27 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA BENEDETTO CROCE 19</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -12947,12 +12947,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -12962,36 +12962,36 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>PV Lonato del Garda</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cassano all'Ionio</t>
+          <t>Lonato del Garda</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>63.18</v>
+        <v>19.27</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -13008,7 +13008,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -13048,93 +13048,93 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -13149,12 +13149,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -13164,36 +13164,36 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>7.2</v>
+        <v>63.18</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -13250,37 +13250,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -13290,48 +13290,48 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>67.84</v>
+        <v>7</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -13351,12 +13351,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -13391,11 +13391,11 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>40.31</v>
+        <v>7.2</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -13412,27 +13412,27 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -13452,12 +13452,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -13492,11 +13492,11 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>14.528</v>
+        <v>67.84</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -13513,17 +13513,17 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -13553,12 +13553,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -13568,36 +13568,36 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>48.5</v>
+        <v>40.31</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -13614,27 +13614,27 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -13654,12 +13654,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -13669,36 +13669,36 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J132" t="n">
-        <v>73.7</v>
+        <v>14.528</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -13715,17 +13715,17 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -13755,12 +13755,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -13780,12 +13780,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -13799,7 +13799,7 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>84.3</v>
+        <v>48.5</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -13816,17 +13816,17 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -13856,88 +13856,88 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>7</v>
+        <v>73.7</v>
       </c>
       <c r="K134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -13957,12 +13957,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -13972,36 +13972,36 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>72</v>
+        <v>84.3</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -14018,17 +14018,17 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -14058,88 +14058,88 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>19.88</v>
+        <v>7</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -14159,12 +14159,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -14174,36 +14174,36 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J137" t="n">
-        <v>19.96</v>
+        <v>72</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -14220,17 +14220,17 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -14260,12 +14260,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14304,7 +14304,7 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>22.925</v>
+        <v>19.88</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -14321,27 +14321,27 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -14361,88 +14361,88 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -14462,12 +14462,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -14477,36 +14477,36 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>46.7235</v>
+        <v>22.925</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -14523,27 +14523,27 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -14563,22 +14563,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -14607,34 +14607,34 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -14664,12 +14664,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -14708,7 +14708,7 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>18.774</v>
+        <v>46.7235</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -14765,12 +14765,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -14780,36 +14780,36 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J143" t="n">
-        <v>20.787</v>
+        <v>2</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -14826,27 +14826,27 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -14866,12 +14866,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -14881,36 +14881,36 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>18.419</v>
+        <v>18.774</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -14927,40 +14927,242 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
+          <t>VIA SENATO 28</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr">
+      <c r="O146" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr">
+      <c r="P146" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q144" t="inlineStr">
+      <c r="Q146" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr">
+      <c r="R146" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
+      <c r="S146" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T144" t="inlineStr">
+      <c r="T146" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U144" t="n">
+      <c r="U146" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14975,7 +15177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U119"/>
+  <dimension ref="A1:U121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22461,12 +22663,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -22476,22 +22678,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Blusolar Chiaravalle</t>
+          <t>PV Novi di Modena</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chiaravalle</t>
+          <t>Novi di Modena</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -22501,11 +22703,11 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>38.16</v>
+        <v>24</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -22522,27 +22724,27 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>VIA CARAVAGGIO 125</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>PESCARA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>65125</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -22562,12 +22764,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -22577,22 +22779,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FOSSATONE</t>
+          <t>Blusolar Chiaravalle</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Massa Lombarda</t>
+          <t>Chiaravalle</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -22606,7 +22808,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>64.67400000000001</v>
+        <v>38.16</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -22623,27 +22825,27 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>VIA PIETRO NENNI 6/E</t>
+          <t>VIA CARAVAGGIO 125</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>PESCARA</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>65125</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -22663,12 +22865,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -22678,22 +22880,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Greppo</t>
+          <t>FOSSATONE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Montepulciano</t>
+          <t>Massa Lombarda</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -22703,11 +22905,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>26.6</v>
+        <v>64.67400000000001</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -22724,27 +22926,27 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>VIALE DELL'ARTE 25</t>
+          <t>VIA PIETRO NENNI 6/E</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -22764,12 +22966,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -22779,36 +22981,36 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Olivola</t>
+          <t>Greppo</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Montepulciano</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>77.98999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -22825,7 +23027,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>VIA ANDREA DORIA 41 G</t>
+          <t>VIALE DELL'ARTE 25</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -22835,7 +23037,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -22865,12 +23067,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -22880,7 +23082,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Olivola</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -22890,12 +23092,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mondragone</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -22909,7 +23111,7 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>18.58</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -22926,27 +23128,27 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA ANDREA DORIA 41 G</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -22966,12 +23168,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -22981,7 +23183,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Francavilla</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -22991,12 +23193,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Mondragone</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -23010,7 +23212,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>48.48</v>
+        <v>18.58</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -23027,27 +23229,27 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>VIA DEL LAURO 9</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -23067,12 +23269,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -23082,7 +23284,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cancello ed Arnone 2</t>
+          <t>Francavilla</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -23092,12 +23294,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23111,7 +23313,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>33.74</v>
+        <v>48.48</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -23128,27 +23330,27 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA DEL LAURO 9</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -23168,12 +23370,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -23183,7 +23385,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>C_023</t>
+          <t>Cancello ed Arnone 2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -23198,7 +23400,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sessa Aurunca</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23212,7 +23414,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>19.021</v>
+        <v>33.74</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -23229,27 +23431,27 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>VIA JULIUS DURST 6</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>BRESSANONE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>39042</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -23269,12 +23471,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -23284,7 +23486,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CASTEL VOLTURNO 2</t>
+          <t>C_023</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -23299,7 +23501,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Castel Volturno</t>
+          <t>Sessa Aurunca</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -23313,7 +23515,7 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>55.26</v>
+        <v>19.021</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -23330,27 +23532,27 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>VIA SANTO STEFANO 11</t>
+          <t>VIA JULIUS DURST 6</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BRESSANONE</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -23370,12 +23572,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -23385,7 +23587,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FV GRAZZANISE</t>
+          <t>CASTEL VOLTURNO 2</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -23400,7 +23602,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Grazzanise</t>
+          <t>Castel Volturno</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -23414,7 +23616,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>21.5</v>
+        <v>55.26</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -23431,27 +23633,27 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>GALLERIA DE CRISTOFORIS 1</t>
+          <t>VIA SANTO STEFANO 11</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -23471,12 +23673,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -23486,36 +23688,36 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Maag Black Sheep</t>
+          <t>FV GRAZZANISE</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Grazzanise</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>11.45</v>
+        <v>21.5</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -23532,23 +23734,27 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>VIA FRANCESCO CRISPI 98</t>
+          <t>GALLERIA DE CRISTOFORIS 1</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>80121</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr"/>
+          <t>20122</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -23568,12 +23774,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -23583,7 +23789,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PV Piegaro</t>
+          <t>Maag Black Sheep</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -23593,26 +23799,26 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Castel Giorgio</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Piegaro</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J86" t="n">
-        <v>9.199999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -23629,27 +23835,23 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>VIA ROMA 151</t>
+          <t>VIA FRANCESCO CRISPI 98</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>BORGO CHIESE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>38083</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
+          <t>80121</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -23669,12 +23871,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -23684,7 +23886,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Agrivoltaico Orvieto</t>
+          <t>PV Piegaro</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -23694,12 +23896,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Orvieto</t>
+          <t>Piegaro</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -23713,7 +23915,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>33.972</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -23730,27 +23932,27 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>VIA GERMANICO 101</t>
+          <t>VIA ROMA 151</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BORGO CHIESE</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -23770,12 +23972,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -23785,7 +23987,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Città della Pieve - Agricola Pievese</t>
+          <t>Agrivoltaico Orvieto</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -23795,26 +23997,26 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Orvieto</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
           <t>Perugia</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Città della Pieve</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Perugia</t>
-        </is>
-      </c>
       <c r="J88" t="n">
-        <v>34.776</v>
+        <v>33.972</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -23831,27 +24033,27 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
+          <t>VIA GERMANICO 101</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -23871,12 +24073,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -23886,7 +24088,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AV1 - Castiglione del Lago Morami</t>
+          <t>Città della Pieve - Agricola Pievese</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -23901,7 +24103,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Castiglione del Lago</t>
+          <t>Città della Pieve</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -23915,7 +24117,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>16.974</v>
+        <v>34.776</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -23932,27 +24134,27 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>VIA BERGAMO 7</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -23972,12 +24174,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -23987,7 +24189,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PV Castel San Giorgio</t>
+          <t>AV1 - Castiglione del Lago Morami</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -23997,12 +24199,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Castel Giorgio</t>
+          <t>Castiglione del Lago</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -24016,7 +24218,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>34.6</v>
+        <v>16.974</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -24033,7 +24235,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>VIA BERGAMO 7</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -24043,7 +24245,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -24053,7 +24255,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -24073,12 +24275,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -24088,7 +24290,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Contrada Fagiolo</t>
+          <t>PV Castel San Giorgio</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -24117,7 +24319,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>55.55</v>
+        <v>34.6</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -24134,7 +24336,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>VIA GALILEO GALILEI 7</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -24144,7 +24346,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -24154,7 +24356,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -24174,12 +24376,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -24189,36 +24391,36 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Casalone</t>
+          <t>Contrada Fagiolo</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Terni</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Castel Giorgio</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>36.3</v>
+        <v>55.55</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -24235,7 +24437,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>VIA AGNELLO 18</t>
+          <t>VIA GALILEO GALILEI 7</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -24245,7 +24447,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -24255,7 +24457,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -24275,12 +24477,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -24290,7 +24492,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Rieti-1</t>
+          <t>Casalone</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -24300,12 +24502,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -24319,7 +24521,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>7</v>
+        <v>36.3</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -24336,7 +24538,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>VIA GABRIO SERBELLONI 5</t>
+          <t>VIA AGNELLO 18</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -24346,7 +24548,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -24391,7 +24593,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Rieti-2</t>
+          <t>Rieti-1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -24420,7 +24622,7 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -24477,12 +24679,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -24492,36 +24694,36 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PV Ferrara</t>
+          <t>Rieti-2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>31.4</v>
+        <v>10</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -24538,27 +24740,27 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>VICOLO DEI GABBIANI 30</t>
+          <t>VIA GABRIO SERBELLONI 5</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -24578,12 +24780,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -24593,7 +24795,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VIGARANO MAINARDA</t>
+          <t>PV Ferrara</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -24608,7 +24810,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Vigarano Mainarda</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -24622,7 +24824,7 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>26.1</v>
+        <v>31.4</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -24639,27 +24841,27 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>VIA BERNINA 7</t>
+          <t>VICOLO DEI GABBIANI 30</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -24679,12 +24881,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -24694,7 +24896,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>PV Codigoro</t>
+          <t>VIGARANO MAINARDA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -24709,7 +24911,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Codigoro</t>
+          <t>Vigarano Mainarda</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -24723,7 +24925,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>24.95</v>
+        <v>26.1</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -24740,27 +24942,27 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -24780,12 +24982,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -24795,7 +24997,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CETA</t>
+          <t>PV Codigoro</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24805,26 +25007,26 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Codigoro</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Crevalcore</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="J98" t="n">
-        <v>89</v>
+        <v>24.95</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -24841,27 +25043,27 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>VIA BERNINA 7</t>
+          <t>VIA BEATO SEBASTIANO VALFRE' 14</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -24881,12 +25083,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -24896,7 +25098,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PV Terre del Reno</t>
+          <t>CETA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -24906,12 +25108,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Terre del Reno</t>
+          <t>Crevalcore</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -24925,44 +25127,44 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>5.4</v>
+        <v>89</v>
       </c>
       <c r="K99" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>VIA GOITO 4</t>
+          <t>VIA BERNINA 7</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>LEGNANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>VR</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -24982,12 +25184,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -24997,7 +25199,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Altedo</t>
+          <t>PV Terre del Reno</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -25007,63 +25209,63 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>Ferrara</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Terre del Reno</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Malalbergo</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="J100" t="n">
-        <v>51.807</v>
+        <v>5.4</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>PIAZZA FRANCESCO CRISPI 1</t>
+          <t>VIA GOITO 4</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>90139</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>VR</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -25083,12 +25285,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -25098,7 +25300,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PV Cento</t>
+          <t>Altedo</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -25113,7 +25315,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pieve di Cento</t>
+          <t>Malalbergo</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -25127,7 +25329,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>2</v>
+        <v>51.807</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -25144,27 +25346,27 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>PIAZZA FRANCESCO CRISPI 1</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>90139</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -25184,12 +25386,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -25199,36 +25401,36 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PV Lonato del Garda</t>
+          <t>PV Cento</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lonato del Garda</t>
+          <t>Pieve di Cento</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>19.27</v>
+        <v>2</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -25245,27 +25447,27 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>VIA ARRIGO BOITO 8</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -25285,12 +25487,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -25300,36 +25502,36 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>Spinazzino</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>19.5</v>
+        <v>26.95</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -25346,27 +25548,27 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA BENEDETTO CROCE 19</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -25386,12 +25588,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -25401,36 +25603,36 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>PV Lonato del Garda</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cassano all'Ionio</t>
+          <t>Lonato del Garda</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>63.18</v>
+        <v>19.27</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -25447,7 +25649,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -25457,7 +25659,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -25467,7 +25669,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -25487,12 +25689,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -25502,36 +25704,36 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -25548,27 +25750,27 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -25588,12 +25790,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -25603,36 +25805,36 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>40.31</v>
+        <v>63.18</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -25649,27 +25851,27 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -25689,12 +25891,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -25704,36 +25906,36 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>48.5</v>
+        <v>7.2</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -25750,17 +25952,17 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -25770,7 +25972,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -25790,12 +25992,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -25805,36 +26007,36 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>73.7</v>
+        <v>40.31</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -25851,27 +26053,27 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -25891,12 +26093,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -25906,7 +26108,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -25916,12 +26118,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -25935,7 +26137,7 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>84.3</v>
+        <v>48.5</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -25952,17 +26154,17 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -25972,7 +26174,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -25992,88 +26194,88 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>7</v>
+        <v>73.7</v>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -26093,12 +26295,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -26108,36 +26310,36 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>72</v>
+        <v>84.3</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -26154,17 +26356,17 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -26174,7 +26376,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -26194,88 +26396,88 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>19.88</v>
+        <v>7</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -26295,12 +26497,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -26310,36 +26512,36 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>19.96</v>
+        <v>72</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -26356,17 +26558,17 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -26376,7 +26578,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -26396,12 +26598,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -26411,7 +26613,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -26426,7 +26628,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -26440,7 +26642,7 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>22.925</v>
+        <v>19.88</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -26457,27 +26659,27 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -26497,88 +26699,88 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -26598,12 +26800,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -26613,36 +26815,36 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>46.7235</v>
+        <v>22.925</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -26659,27 +26861,27 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -26699,22 +26901,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -26743,34 +26945,34 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -26800,12 +27002,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -26815,7 +27017,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -26830,7 +27032,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -26844,7 +27046,7 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>18.774</v>
+        <v>46.7235</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -26861,7 +27063,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -26901,12 +27103,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -26916,36 +27118,36 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>20.787</v>
+        <v>2</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -26962,40 +27164,242 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
+          <t>STRADA STATALE 28 SUD 14</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>MONDOVI</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>12084</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Lombardore</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>18.774</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>VIA SENATO 28</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
           <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr">
+      <c r="O121" t="inlineStr">
         <is>
           <t>TORINO</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
+      <c r="P121" t="inlineStr">
         <is>
           <t>10153</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr">
+      <c r="Q121" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
+      <c r="R121" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
+      <c r="S121" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="T121" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U119" t="n">
+      <c r="U121" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29652,7 +30056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30740,14 +31144,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>26.6</v>
+        <v>26.95</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -30756,19 +31160,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>24.95</v>
+        <v>26.6</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -30782,14 +31186,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>22.925</v>
+        <v>24.95</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -30798,19 +31202,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>22.57</v>
+        <v>24</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -30824,14 +31228,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>20.787</v>
+        <v>22.925</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -30840,40 +31244,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>20</v>
+        <v>22.57</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>19.96</v>
+        <v>20.787</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -30882,40 +31286,40 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>19.88</v>
+        <v>20</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>19.5</v>
+        <v>19.96</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -30924,19 +31328,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>19.27</v>
+        <v>19.88</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -30945,19 +31349,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>19.021</v>
+        <v>19.5</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -30966,19 +31370,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>18.419</v>
+        <v>19.27</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -30987,19 +31391,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>16.974</v>
+        <v>19.021</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -31008,19 +31412,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>16.63</v>
+        <v>18.419</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -31029,19 +31433,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>14.528</v>
+        <v>16.974</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -31050,40 +31454,40 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>14</v>
+        <v>16.63</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>13.56</v>
+        <v>14.528</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -31092,40 +31496,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>11.45</v>
+        <v>14</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>9.199999999999999</v>
+        <v>13.56</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -31134,19 +31538,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>7.2</v>
+        <v>11.45</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -31155,19 +31559,19 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -31176,19 +31580,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
@@ -31197,19 +31601,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -31218,40 +31622,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -31260,40 +31664,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0.93</v>
+        <v>5.4</v>
       </c>
       <c r="E78" t="n">
         <v>1</v>
@@ -31302,19 +31706,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
@@ -31323,21 +31727,63 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>Bergamo</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Livorno</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>Lucca</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="n">
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
         <v>0.5</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31374,7 +31820,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
@@ -31384,7 +31830,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6217.0645</v>
+        <v>6268.0145</v>
       </c>
     </row>
     <row r="4">
@@ -31404,7 +31850,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -31766,40 +32212,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ragusa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>125.6</v>
+        <v>128.01</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Ragusa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>104.01</v>
+        <v>125.6</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -31808,43 +32254,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Oristano</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>93.45999999999999</v>
+        <v>114.8</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Oristano</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>87.84999999999999</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -32520,13 +32966,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>2366.6445</v>
+        <v>2390.6445</v>
       </c>
     </row>
     <row r="3">
@@ -32536,13 +32982,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>767.684</v>
+        <v>794.634</v>
       </c>
     </row>
     <row r="4">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U173"/>
+  <dimension ref="A1:U174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15270,12 +15270,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -15285,36 +15285,36 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>PV Lonato del Garda</t>
+          <t>PV Mesola</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lonato del Garda</t>
+          <t>Mesola</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>19.27</v>
+        <v>17.91</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>VIA ARRIGO BOITO 8</t>
+          <t>PIAZZA SAN SEPOLCRO 1</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -15371,12 +15371,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -15386,36 +15386,36 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Lonato del Garda</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Lonato del Garda</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J149" t="n">
-        <v>19.5</v>
+        <v>19.27</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -15432,27 +15432,27 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -15472,12 +15472,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -15487,7 +15487,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -15497,26 +15497,26 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J150" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -15533,27 +15533,27 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -15573,12 +15573,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>PV Altomonte e Castrovillari</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Altomonte</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>77.7</v>
+        <v>63.18</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -15674,93 +15674,93 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>PV Altomonte e Castrovillari</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Altomonte</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>7</v>
+        <v>77.7</v>
       </c>
       <c r="K152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
@@ -15775,37 +15775,37 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -15815,53 +15815,53 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
@@ -15876,12 +15876,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -15916,11 +15916,11 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>67.84</v>
+        <v>7.2</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
@@ -15977,12 +15977,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -16002,12 +16002,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -16017,11 +16017,11 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>40.31</v>
+        <v>67.84</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -16038,32 +16038,32 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
@@ -16078,12 +16078,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -16122,7 +16122,7 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>14.528</v>
+        <v>40.31</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -16139,32 +16139,32 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
@@ -16179,12 +16179,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -16194,36 +16194,36 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>48.5</v>
+        <v>14.528</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -16240,17 +16240,17 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T157" t="inlineStr">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -16305,12 +16305,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -16381,12 +16381,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -16442,17 +16442,17 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -16482,12 +16482,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -16512,7 +16512,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -16526,7 +16526,7 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>36.32</v>
+        <v>84.3</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -16543,27 +16543,27 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -16583,88 +16583,88 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>7</v>
+        <v>36.32</v>
       </c>
       <c r="K161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
@@ -16684,22 +16684,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -16709,63 +16709,63 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J162" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -16785,12 +16785,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -16800,36 +16800,36 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -16846,27 +16846,27 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
@@ -16886,12 +16886,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -16930,7 +16930,7 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -16947,27 +16947,27 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -16987,12 +16987,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -17031,7 +17031,7 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -17048,27 +17048,27 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
@@ -17088,88 +17088,88 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
+          <t>Potenza</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Melfi</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Salerno</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>22.925</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>VIA LUIGI BUZZI 6</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>CASALE MONFERRATO</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>15033</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
           <t>Torino</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Pinerolo</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Nord Ovest</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="J166" t="n">
-        <v>12</v>
-      </c>
-      <c r="K166" t="n">
-        <v>1</v>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>Attivo</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>Costruzione</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>VIA MATTATOIO 3</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>SALUZZO</t>
-        </is>
-      </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>12037</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>Cuneo</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -17189,22 +17189,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -17233,44 +17233,44 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -17290,12 +17290,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -17305,7 +17305,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -17334,7 +17334,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -17351,27 +17351,27 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
@@ -17391,12 +17391,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -17421,7 +17421,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -17435,7 +17435,7 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -17452,27 +17452,27 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
@@ -17492,22 +17492,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -17517,12 +17517,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -17536,10 +17536,10 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>18</v>
+        <v>18.774</v>
       </c>
       <c r="K170" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -17548,32 +17548,32 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -17593,54 +17593,54 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>96.09</v>
+        <v>18</v>
       </c>
       <c r="K171" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -17649,32 +17649,32 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
@@ -17694,12 +17694,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -17709,22 +17709,22 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Maniago</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -17734,11 +17734,11 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>20.787</v>
+        <v>96.09</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -17755,27 +17755,27 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -17795,12 +17795,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -17810,36 +17810,36 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>18.419</v>
+        <v>20.787</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -17856,40 +17856,141 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O173" t="inlineStr">
+      <c r="O174" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P173" t="inlineStr">
+      <c r="P174" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q173" t="inlineStr">
+      <c r="Q174" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R173" t="inlineStr">
+      <c r="R174" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S173" t="inlineStr">
+      <c r="S174" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T173" t="inlineStr">
+      <c r="T174" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U173" t="n">
+      <c r="U174" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17904,7 +18005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U147"/>
+  <dimension ref="A1:U148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30537,12 +30638,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -30552,36 +30653,36 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>PV Lonato del Garda</t>
+          <t>PV Mesola</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lonato del Garda</t>
+          <t>Mesola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>19.27</v>
+        <v>17.91</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -30598,7 +30699,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>VIA ARRIGO BOITO 8</t>
+          <t>PIAZZA SAN SEPOLCRO 1</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -30608,7 +30709,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -30638,12 +30739,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -30653,36 +30754,36 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Lonato del Garda</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Lonato del Garda</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>19.5</v>
+        <v>19.27</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -30699,27 +30800,27 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -30739,12 +30840,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -30754,7 +30855,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -30764,26 +30865,26 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J128" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -30800,27 +30901,27 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -30840,12 +30941,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -30855,7 +30956,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>PV Altomonte e Castrovillari</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -30870,7 +30971,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Altomonte</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -30884,7 +30985,7 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>77.7</v>
+        <v>63.18</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -30941,12 +31042,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -30956,36 +31057,36 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>PV Altomonte e Castrovillari</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Altomonte</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>7.2</v>
+        <v>77.7</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -31002,7 +31103,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -31012,7 +31113,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -31022,7 +31123,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -31042,12 +31143,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -31057,7 +31158,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -31067,12 +31168,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -31082,11 +31183,11 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>40.31</v>
+        <v>7.2</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -31103,27 +31204,27 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -31143,12 +31244,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -31158,36 +31259,36 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J132" t="n">
-        <v>48.5</v>
+        <v>40.31</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -31204,27 +31305,27 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -31259,7 +31360,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -31269,12 +31370,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -31288,7 +31389,7 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -31345,12 +31446,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -31360,7 +31461,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -31375,7 +31476,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -31389,7 +31490,7 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -31406,17 +31507,17 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -31426,7 +31527,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -31446,12 +31547,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -31461,7 +31562,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -31476,7 +31577,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -31490,7 +31591,7 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>36.32</v>
+        <v>84.3</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -31507,27 +31608,27 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -31547,88 +31648,88 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>7</v>
+        <v>36.32</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -31648,22 +31749,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -31673,63 +31774,63 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J137" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -31749,12 +31850,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -31764,36 +31865,36 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J138" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -31810,27 +31911,27 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -31850,12 +31951,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -31865,7 +31966,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -31894,7 +31995,7 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -31911,27 +32012,27 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -31951,12 +32052,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -31966,7 +32067,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -31981,7 +32082,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -31995,7 +32096,7 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -32012,27 +32113,27 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -32052,88 +32153,88 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
+          <t>Potenza</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Melfi</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Salerno</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>22.925</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>VIA LUIGI BUZZI 6</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>CASALE MONFERRATO</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>15033</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
           <t>Torino</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Pinerolo</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Nord Ovest</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="J141" t="n">
-        <v>12</v>
-      </c>
-      <c r="K141" t="n">
-        <v>1</v>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>Attivo</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>Costruzione</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>VIA MATTATOIO 3</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>SALUZZO</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>12037</t>
-        </is>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>Cuneo</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -32153,22 +32254,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -32183,7 +32284,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -32197,44 +32298,44 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -32254,12 +32355,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -32269,7 +32370,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -32284,7 +32385,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -32298,7 +32399,7 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -32315,27 +32416,27 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -32355,12 +32456,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -32370,7 +32471,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -32385,7 +32486,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -32399,7 +32500,7 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -32416,27 +32517,27 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -32456,22 +32557,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -32481,12 +32582,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -32500,10 +32601,10 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>18</v>
+        <v>18.774</v>
       </c>
       <c r="K145" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -32512,32 +32613,32 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -32557,54 +32658,54 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>96.09</v>
+        <v>18</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -32613,32 +32714,32 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -32658,12 +32759,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -32673,22 +32774,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Maniago</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -32698,11 +32799,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>20.787</v>
+        <v>96.09</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -32719,40 +32820,141 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>BOLZANO</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>39100</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
           <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr">
+      <c r="O148" t="inlineStr">
         <is>
           <t>TORINO</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr">
+      <c r="P148" t="inlineStr">
         <is>
           <t>10153</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr">
+      <c r="Q148" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr">
+      <c r="R148" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
+      <c r="S148" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr">
+      <c r="T148" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U147" t="n">
+      <c r="U148" t="n">
         <v>1</v>
       </c>
     </row>
@@ -36593,40 +36795,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>36.32</v>
+        <v>40.287</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>34.776</v>
+        <v>36.32</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -36635,7 +36837,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -36647,7 +36849,7 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>34.6</v>
+        <v>34.776</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -36656,7 +36858,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -36668,7 +36870,7 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>33.972</v>
+        <v>34.6</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -36677,19 +36879,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>33.527</v>
+        <v>33.972</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -36698,19 +36900,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>31.4</v>
+        <v>33.527</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -36719,85 +36921,85 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>30.148</v>
+        <v>31.4</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>28.3</v>
+        <v>30.148</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>28.209</v>
+        <v>28.3</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>26.95</v>
+        <v>28.209</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -36808,14 +37010,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>26.6</v>
+        <v>26.95</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -36824,19 +37026,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>24.95</v>
+        <v>26.6</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -36845,7 +37047,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -36854,52 +37056,52 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>24.77</v>
+        <v>24.95</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>24</v>
+        <v>24.77</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>22.925</v>
+        <v>24</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -36908,19 +37110,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>22.57</v>
+        <v>22.925</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -36929,19 +37131,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>22.377</v>
+        <v>22.57</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -37526,7 +37728,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
@@ -37536,7 +37738,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7581.443499999999</v>
+        <v>7599.353499999999</v>
       </c>
     </row>
     <row r="4">
@@ -37556,7 +37758,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -37876,85 +38078,85 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Caserta</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>148.101</v>
+        <v>154.738</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Caserta</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>146.807</v>
+        <v>148.101</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Terni</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>140.88</v>
+        <v>146.807</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>136.828</v>
+        <v>140.88</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -38777,13 +38979,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
-        <v>2764.0935</v>
+        <v>2782.0035</v>
       </c>
     </row>
     <row r="3">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U208"/>
+  <dimension ref="A1:U209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18401,12 +18401,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -18416,36 +18416,36 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>Lonato</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Bedizzole</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>19.5</v>
+        <v>23.2</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -18462,27 +18462,27 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -18502,12 +18502,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -18517,7 +18517,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -18527,26 +18527,26 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J180" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -18563,27 +18563,27 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
@@ -18603,12 +18603,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>PV Altomonte e Castrovillari</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Altomonte</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -18647,7 +18647,7 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>77.7</v>
+        <v>63.18</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -18704,12 +18704,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -18719,7 +18719,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>PV Altomonte e Castrovillari</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -18729,12 +18729,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>San Mauro Marchesato</t>
+          <t>Altomonte</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -18748,7 +18748,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>17.726</v>
+        <v>77.7</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -18765,27 +18765,27 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>VIA PAOLO EMILIO 10</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -18805,68 +18805,68 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>San Mauro Marchesato</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>7</v>
+        <v>17.726</v>
       </c>
       <c r="K183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA PAOLO EMILIO 10</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -18886,12 +18886,12 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
@@ -18906,37 +18906,37 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -18946,53 +18946,53 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J184" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
@@ -19007,12 +19007,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -19022,7 +19022,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -19032,12 +19032,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -19047,11 +19047,11 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J185" t="n">
-        <v>67.84</v>
+        <v>7.2</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
@@ -19108,12 +19108,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -19123,7 +19123,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -19133,12 +19133,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -19148,11 +19148,11 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J186" t="n">
-        <v>40.31</v>
+        <v>67.84</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -19169,32 +19169,32 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
@@ -19209,12 +19209,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -19224,7 +19224,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>14.528</v>
+        <v>40.31</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -19270,32 +19270,32 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
@@ -19310,12 +19310,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -19325,7 +19325,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Scaldasole 41</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Scaldasole</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -19354,7 +19354,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>37.16</v>
+        <v>14.528</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -19371,17 +19371,17 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -19411,12 +19411,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -19426,36 +19426,36 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>Scaldasole 41</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Scaldasole</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J189" t="n">
-        <v>48.5</v>
+        <v>37.16</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -19472,17 +19472,17 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
@@ -19492,12 +19492,12 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
@@ -19527,7 +19527,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -19537,12 +19537,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -19556,7 +19556,7 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -19613,12 +19613,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -19674,17 +19674,17 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
@@ -19714,12 +19714,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -19729,7 +19729,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>36.32</v>
+        <v>84.3</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -19775,27 +19775,27 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -19815,12 +19815,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -19830,7 +19830,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -19859,7 +19859,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>29.73</v>
+        <v>36.32</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -19876,27 +19876,27 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
@@ -19916,88 +19916,88 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>7</v>
+        <v>29.73</v>
       </c>
       <c r="K194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
@@ -20017,22 +20017,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -20042,63 +20042,63 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J195" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
@@ -20118,12 +20118,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -20133,36 +20133,36 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -20179,27 +20179,27 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
@@ -20219,12 +20219,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -20263,7 +20263,7 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K197" t="n">
         <v>0</v>
@@ -20280,27 +20280,27 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -20320,12 +20320,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -20381,27 +20381,27 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -20421,12 +20421,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -20436,7 +20436,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -20465,7 +20465,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>19.968</v>
+        <v>22.925</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -20482,27 +20482,27 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
@@ -20522,12 +20522,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -20566,7 +20566,7 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -20583,27 +20583,27 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -20623,88 +20623,88 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J201" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
@@ -20724,22 +20724,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -20768,44 +20768,44 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
@@ -20825,12 +20825,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -20840,7 +20840,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -20869,7 +20869,7 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -20886,27 +20886,27 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
@@ -20926,12 +20926,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -20941,7 +20941,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -20956,7 +20956,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -20970,7 +20970,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -20987,27 +20987,27 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
@@ -21027,22 +21027,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -21052,12 +21052,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -21071,10 +21071,10 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>18</v>
+        <v>18.774</v>
       </c>
       <c r="K205" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -21083,32 +21083,32 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
@@ -21128,54 +21128,54 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J206" t="n">
-        <v>96.09</v>
+        <v>18</v>
       </c>
       <c r="K206" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -21184,32 +21184,32 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
@@ -21229,12 +21229,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -21244,22 +21244,22 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Maniago</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -21269,11 +21269,11 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J207" t="n">
-        <v>20.787</v>
+        <v>96.09</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -21290,27 +21290,27 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -21330,12 +21330,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -21345,36 +21345,36 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J208" t="n">
-        <v>18.419</v>
+        <v>20.787</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -21391,40 +21391,141 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U208" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O208" t="inlineStr">
+      <c r="O209" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P208" t="inlineStr">
+      <c r="P209" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q208" t="inlineStr">
+      <c r="Q209" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R208" t="inlineStr">
+      <c r="R209" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S208" t="inlineStr">
+      <c r="S209" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T208" t="inlineStr">
+      <c r="T209" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U208" t="n">
+      <c r="U209" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21439,7 +21540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U179"/>
+  <dimension ref="A1:U180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37001,12 +37102,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -37016,36 +37117,36 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>Lonato</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Bedizzole</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>19.5</v>
+        <v>23.2</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -37062,27 +37163,27 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -37102,12 +37203,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -37117,7 +37218,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -37127,26 +37228,26 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J156" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -37163,27 +37264,27 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -37203,12 +37304,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -37218,7 +37319,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>PV Altomonte e Castrovillari</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -37233,7 +37334,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Altomonte</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -37247,7 +37348,7 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>77.7</v>
+        <v>63.18</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -37304,12 +37405,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -37319,7 +37420,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>PV Altomonte e Castrovillari</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -37329,12 +37430,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>San Mauro Marchesato</t>
+          <t>Altomonte</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -37348,7 +37449,7 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>17.726</v>
+        <v>77.7</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -37365,27 +37466,27 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>VIA PAOLO EMILIO 10</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
@@ -37405,12 +37506,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -37420,36 +37521,36 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>San Mauro Marchesato</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J159" t="n">
-        <v>7.2</v>
+        <v>17.726</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -37466,27 +37567,27 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA PAOLO EMILIO 10</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -37506,12 +37607,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -37521,7 +37622,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -37531,12 +37632,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -37546,11 +37647,11 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>40.31</v>
+        <v>7.2</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -37567,27 +37668,27 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -37607,12 +37708,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -37622,36 +37723,36 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>48.5</v>
+        <v>40.31</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -37668,27 +37769,27 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
@@ -37723,7 +37824,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -37733,12 +37834,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -37752,7 +37853,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -37809,12 +37910,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -37824,7 +37925,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -37839,7 +37940,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -37853,7 +37954,7 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -37870,17 +37971,17 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -37890,7 +37991,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
@@ -37910,12 +38011,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -37925,7 +38026,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -37940,7 +38041,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -37954,7 +38055,7 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>36.32</v>
+        <v>84.3</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -37971,27 +38072,27 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -38011,12 +38112,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -38026,7 +38127,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -38041,7 +38142,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -38055,7 +38156,7 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>29.73</v>
+        <v>36.32</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -38072,27 +38173,27 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
@@ -38112,88 +38213,88 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J166" t="n">
-        <v>7</v>
+        <v>29.73</v>
       </c>
       <c r="K166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -38213,22 +38314,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -38238,63 +38339,63 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J167" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -38314,12 +38415,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -38329,36 +38430,36 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>19.88</v>
+        <v>72</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -38375,27 +38476,27 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
@@ -38415,12 +38516,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -38430,7 +38531,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -38459,7 +38560,7 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -38476,27 +38577,27 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
@@ -38516,12 +38617,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -38531,7 +38632,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -38546,7 +38647,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -38560,7 +38661,7 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -38577,27 +38678,27 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -38617,12 +38718,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -38632,7 +38733,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -38647,7 +38748,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -38661,7 +38762,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>19.968</v>
+        <v>22.925</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -38678,27 +38779,27 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
@@ -38718,12 +38819,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -38733,7 +38834,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -38748,7 +38849,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -38762,7 +38863,7 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -38779,27 +38880,27 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -38819,88 +38920,88 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -38920,22 +39021,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -38950,7 +39051,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -38964,44 +39065,44 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
@@ -39021,12 +39122,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -39036,7 +39137,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -39051,7 +39152,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -39065,7 +39166,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -39082,27 +39183,27 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -39122,12 +39223,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -39137,7 +39238,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -39152,7 +39253,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -39166,7 +39267,7 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
@@ -39183,27 +39284,27 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -39223,22 +39324,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -39248,12 +39349,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -39267,10 +39368,10 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>18</v>
+        <v>18.774</v>
       </c>
       <c r="K177" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -39279,32 +39380,32 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -39324,54 +39425,54 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>96.09</v>
+        <v>18</v>
       </c>
       <c r="K178" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -39380,32 +39481,32 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
@@ -39425,12 +39526,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -39440,22 +39541,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Maniago</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -39465,11 +39566,11 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>20.787</v>
+        <v>96.09</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -39486,40 +39587,141 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>BOLZANO</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>39100</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
           <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
-      <c r="O179" t="inlineStr">
+      <c r="O180" t="inlineStr">
         <is>
           <t>TORINO</t>
         </is>
       </c>
-      <c r="P179" t="inlineStr">
+      <c r="P180" t="inlineStr">
         <is>
           <t>10153</t>
         </is>
       </c>
-      <c r="Q179" t="inlineStr">
+      <c r="Q180" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="R179" t="inlineStr">
+      <c r="R180" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="S179" t="inlineStr">
+      <c r="S180" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr">
+      <c r="T180" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U179" t="n">
+      <c r="U180" t="n">
         <v>1</v>
       </c>
     </row>
@@ -42580,7 +42782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44230,19 +44432,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>22.925</v>
+        <v>23.2</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
@@ -44251,19 +44453,19 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>22.57</v>
+        <v>22.925</v>
       </c>
       <c r="E80" t="n">
         <v>1</v>
@@ -44272,19 +44474,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>20.787</v>
+        <v>22.57</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -44293,49 +44495,49 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>20</v>
+        <v>20.787</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>19.968</v>
+        <v>20</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -44347,7 +44549,7 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -44356,19 +44558,19 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>19.5</v>
+        <v>19.96</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -44377,19 +44579,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>19.27</v>
+        <v>19.5</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -44398,19 +44600,19 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>19.021</v>
+        <v>19.27</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -44419,19 +44621,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>18.419</v>
+        <v>19.021</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -44440,19 +44642,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>18</v>
+        <v>18.419</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -44461,19 +44663,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -44482,19 +44684,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>17.726</v>
+        <v>17.8</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
@@ -44503,19 +44705,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>16.63</v>
+        <v>17.726</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -44524,7 +44726,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -44536,7 +44738,7 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>14.03</v>
+        <v>16.63</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -44545,61 +44747,61 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>13.56</v>
+        <v>14</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>12</v>
+        <v>13.56</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
@@ -44608,19 +44810,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>11.45</v>
+        <v>12</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -44629,7 +44831,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -44641,7 +44843,7 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>9.199999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
@@ -44650,19 +44852,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>8.984</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E99" t="n">
         <v>1</v>
@@ -44671,19 +44873,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>7.2</v>
+        <v>8.984</v>
       </c>
       <c r="E100" t="n">
         <v>1</v>
@@ -44692,19 +44894,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>7.02</v>
+        <v>7.2</v>
       </c>
       <c r="E101" t="n">
         <v>1</v>
@@ -44713,19 +44915,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -44739,7 +44941,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -44755,19 +44957,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
@@ -44776,43 +44978,43 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="E105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -44823,14 +45025,14 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
         <v>1</v>
@@ -44839,19 +45041,19 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0.93</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -44860,19 +45062,19 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -44886,7 +45088,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -44896,6 +45098,27 @@
         <v>0.5</v>
       </c>
       <c r="E110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Lucca</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E111" t="n">
         <v>1</v>
       </c>
     </row>
@@ -44932,7 +45155,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3">
@@ -44942,7 +45165,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8906.147499999999</v>
+        <v>8929.3475</v>
       </c>
     </row>
     <row r="4">
@@ -44962,7 +45185,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -45870,103 +46093,103 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>38.754</v>
+        <v>42.47</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>38.535</v>
+        <v>38.754</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>38.16</v>
+        <v>38.535</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>37.226</v>
+        <v>38.16</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>37.2</v>
+        <v>37.226</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
@@ -45975,106 +46198,106 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pesaro e Urbino</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>28.38</v>
+        <v>37.2</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Pesaro e Urbino</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>24.82</v>
+        <v>28.38</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>20.787</v>
+        <v>24.82</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>19.995</v>
+        <v>20.787</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>19.27</v>
+        <v>19.995</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -46257,13 +46480,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>984.794</v>
+        <v>1007.994</v>
       </c>
     </row>
     <row r="5">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U209"/>
+  <dimension ref="A1:U211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19512,12 +19512,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -19527,36 +19527,36 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PV Alessandria</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J190" t="n">
-        <v>48.5</v>
+        <v>5</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -19568,32 +19568,32 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
@@ -19613,12 +19613,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -19628,36 +19628,36 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>PV Tortona</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Tortona</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>73.7</v>
+        <v>10</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -19674,27 +19674,27 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
@@ -19714,12 +19714,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -19729,7 +19729,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -19739,12 +19739,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>84.3</v>
+        <v>48.5</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -19775,17 +19775,17 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -19815,12 +19815,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -19830,7 +19830,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -19859,7 +19859,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>36.32</v>
+        <v>73.7</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -19876,27 +19876,27 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
@@ -19916,12 +19916,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -19960,7 +19960,7 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>29.73</v>
+        <v>84.3</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -20017,88 +20017,88 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>7</v>
+        <v>36.32</v>
       </c>
       <c r="K195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
@@ -20118,12 +20118,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -20133,36 +20133,36 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>72</v>
+        <v>29.73</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -20179,17 +20179,17 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
@@ -20219,88 +20219,88 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>19.88</v>
+        <v>7</v>
       </c>
       <c r="K197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -20320,12 +20320,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -20335,36 +20335,36 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>19.96</v>
+        <v>72</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -20381,17 +20381,17 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -20421,12 +20421,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -20436,7 +20436,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -20465,7 +20465,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>22.925</v>
+        <v>19.88</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -20482,27 +20482,27 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
@@ -20522,12 +20522,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -20566,7 +20566,7 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>19.968</v>
+        <v>19.96</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -20583,17 +20583,17 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -20603,7 +20603,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -20623,12 +20623,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -20638,7 +20638,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -20667,7 +20667,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>19.96</v>
+        <v>22.925</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -20684,27 +20684,27 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
@@ -20724,88 +20724,88 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J202" t="n">
-        <v>12</v>
+        <v>19.968</v>
       </c>
       <c r="K202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
@@ -20825,12 +20825,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -20840,36 +20840,36 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J203" t="n">
-        <v>46.7235</v>
+        <v>19.96</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -20886,27 +20886,27 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
@@ -20926,22 +20926,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -20970,34 +20970,34 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
@@ -21027,12 +21027,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -21057,7 +21057,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -21071,7 +21071,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>18.774</v>
+        <v>46.7235</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -21128,22 +21128,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -21153,12 +21153,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -21172,10 +21172,10 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K206" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -21184,32 +21184,32 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
@@ -21229,12 +21229,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -21244,36 +21244,36 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J207" t="n">
-        <v>96.09</v>
+        <v>18.774</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -21290,27 +21290,27 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -21330,54 +21330,54 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J208" t="n">
-        <v>20.787</v>
+        <v>18</v>
       </c>
       <c r="K208" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -21386,32 +21386,32 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
@@ -21431,12 +21431,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -21446,36 +21446,36 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Maniago</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J209" t="n">
-        <v>18.419</v>
+        <v>96.09</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -21492,40 +21492,242 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>BOLZANO</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>39100</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U209" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U210" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O209" t="inlineStr">
+      <c r="O211" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P209" t="inlineStr">
+      <c r="P211" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q209" t="inlineStr">
+      <c r="Q211" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R209" t="inlineStr">
+      <c r="R211" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S209" t="inlineStr">
+      <c r="S211" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T209" t="inlineStr">
+      <c r="T211" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U209" t="n">
+      <c r="U211" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21540,7 +21742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U180"/>
+  <dimension ref="A1:U182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37809,12 +38011,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -37824,36 +38026,36 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PV Alessandria</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>48.5</v>
+        <v>5</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -37865,32 +38067,32 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -37910,12 +38112,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -37925,36 +38127,36 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>PV Tortona</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Tortona</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>73.7</v>
+        <v>10</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -37971,27 +38173,27 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
@@ -38011,12 +38213,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -38026,7 +38228,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -38036,12 +38238,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -38055,7 +38257,7 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>84.3</v>
+        <v>48.5</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -38072,17 +38274,17 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -38092,7 +38294,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -38112,12 +38314,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -38127,7 +38329,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -38142,7 +38344,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -38156,7 +38358,7 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>36.32</v>
+        <v>73.7</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -38173,27 +38375,27 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
@@ -38213,12 +38415,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -38228,7 +38430,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -38243,7 +38445,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -38257,7 +38459,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>29.73</v>
+        <v>84.3</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -38274,7 +38476,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -38284,7 +38486,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -38314,88 +38516,88 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J167" t="n">
-        <v>7</v>
+        <v>36.32</v>
       </c>
       <c r="K167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -38415,12 +38617,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -38430,36 +38632,36 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>72</v>
+        <v>29.73</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -38476,17 +38678,17 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -38496,7 +38698,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
@@ -38516,88 +38718,88 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>19.88</v>
+        <v>7</v>
       </c>
       <c r="K169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
@@ -38617,12 +38819,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -38632,36 +38834,36 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>19.96</v>
+        <v>72</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -38678,17 +38880,17 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -38698,7 +38900,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -38718,12 +38920,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -38733,7 +38935,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -38748,7 +38950,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -38762,7 +38964,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>22.925</v>
+        <v>19.88</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -38779,27 +38981,27 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
@@ -38819,12 +39021,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -38834,7 +39036,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -38849,7 +39051,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -38863,7 +39065,7 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>19.968</v>
+        <v>19.96</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -38880,17 +39082,17 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
@@ -38900,7 +39102,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -38920,12 +39122,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -38935,7 +39137,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -38950,7 +39152,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -38964,7 +39166,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>19.96</v>
+        <v>22.925</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -38981,27 +39183,27 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -39021,88 +39223,88 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J174" t="n">
-        <v>12</v>
+        <v>19.968</v>
       </c>
       <c r="K174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
@@ -39122,12 +39324,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -39137,36 +39339,36 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>46.7235</v>
+        <v>19.96</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -39183,27 +39385,27 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -39223,22 +39425,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -39267,34 +39469,34 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
@@ -39324,12 +39526,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -39339,7 +39541,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -39354,7 +39556,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -39368,7 +39570,7 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>18.774</v>
+        <v>46.7235</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -39385,7 +39587,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -39425,22 +39627,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -39450,12 +39652,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -39469,10 +39671,10 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K178" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -39481,32 +39683,32 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
@@ -39526,12 +39728,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -39541,36 +39743,36 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>96.09</v>
+        <v>18.774</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -39587,27 +39789,27 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -39627,101 +39829,303 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>PV Maserano</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Biella</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Masserano</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>18</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>VIA VARALLO POMBIA 44</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>CASTELLETTO SOPRA TICINO</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>28053</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Maniago Solar 1- ELLO 11</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Friuli-Venezia Giulia</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Pordenone</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Maniago</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>BOLZANO</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>39100</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>FLYSUN 10 SRL</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>FLYSUN 10 SRL</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>PV PORTOGRUARO</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>Veneto</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>Venezia</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G182" t="inlineStr">
         <is>
           <t>Portogruaro</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H182" t="inlineStr">
         <is>
           <t>Nord Est</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="I182" t="inlineStr">
         <is>
           <t>Venezia</t>
         </is>
       </c>
-      <c r="J180" t="n">
+      <c r="J182" t="n">
         <v>20.787</v>
       </c>
-      <c r="K180" t="n">
+      <c r="K182" t="n">
         <v>0</v>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t>In pipeline</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t>Autorizzazioni</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr">
+      <c r="N182" t="inlineStr">
         <is>
           <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr">
+      <c r="O182" t="inlineStr">
         <is>
           <t>TORINO</t>
         </is>
       </c>
-      <c r="P180" t="inlineStr">
+      <c r="P182" t="inlineStr">
         <is>
           <t>10153</t>
         </is>
       </c>
-      <c r="Q180" t="inlineStr">
+      <c r="Q182" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="R180" t="inlineStr">
+      <c r="R182" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="S180" t="inlineStr">
+      <c r="S182" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T180" t="inlineStr">
+      <c r="T182" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U180" t="n">
+      <c r="U182" t="n">
         <v>1</v>
       </c>
     </row>
@@ -42782,7 +43186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44747,19 +45151,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>14.03</v>
+        <v>15</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -44768,61 +45172,61 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>13.56</v>
+        <v>14</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>12</v>
+        <v>13.56</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -44831,19 +45235,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>11.45</v>
+        <v>12</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
@@ -44852,7 +45256,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -44864,7 +45268,7 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>9.199999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="E99" t="n">
         <v>1</v>
@@ -44873,19 +45277,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>8.984</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E100" t="n">
         <v>1</v>
@@ -44894,19 +45298,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>7.2</v>
+        <v>8.984</v>
       </c>
       <c r="E101" t="n">
         <v>1</v>
@@ -44915,19 +45319,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>7.02</v>
+        <v>7.2</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -44936,19 +45340,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
@@ -44962,7 +45366,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -44978,19 +45382,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
@@ -44999,43 +45403,43 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="E106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -45046,14 +45450,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -45062,19 +45466,19 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>0.93</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -45083,19 +45487,19 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
@@ -45109,7 +45513,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -45119,6 +45523,27 @@
         <v>0.5</v>
       </c>
       <c r="E111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Lucca</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E112" t="n">
         <v>1</v>
       </c>
     </row>
@@ -45155,7 +45580,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3">
@@ -45165,7 +45590,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8929.3475</v>
+        <v>8944.3475</v>
       </c>
     </row>
     <row r="4">
@@ -45185,7 +45610,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -45199,7 +45624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46345,63 +46770,84 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>7.2</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>Monza e della Brianza</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Lombardia</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Piacenza</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="n">
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
         <v>7</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -46496,13 +46942,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>328.035</v>
+        <v>343.035</v>
       </c>
     </row>
     <row r="6">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U211"/>
+  <dimension ref="A1:U214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18300,12 +18300,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -18315,36 +18315,36 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>PV Lonato del Garda</t>
+          <t>PV Espe-1</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lonato del Garda</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>19.27</v>
+        <v>12</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -18356,32 +18356,32 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>VIA ARRIGO BOITO 8</t>
+          <t>VIA DELL'ARTIGIANATO 6</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>GRANTORTO</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>35010</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
@@ -18401,12 +18401,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -18416,36 +18416,36 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Lonato</t>
+          <t>PV Espe-2</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bedizzole</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>23.2</v>
+        <v>10</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -18457,32 +18457,32 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
+          <t>VIA DELL'ARTIGIANATO 6</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>GRANTORTO</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>35010</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -18502,12 +18502,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -18517,36 +18517,36 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Lonato del Garda</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Lonato del Garda</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>19.5</v>
+        <v>19.27</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -18563,27 +18563,27 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
@@ -18603,12 +18603,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -18618,36 +18618,36 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Lonato</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cassano all'Ionio</t>
+          <t>Bedizzole</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>63.18</v>
+        <v>23.2</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -18664,27 +18664,27 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -18704,12 +18704,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -18719,7 +18719,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>PV Altomonte e Castrovillari</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -18729,26 +18729,26 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Altomonte</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J182" t="n">
-        <v>77.7</v>
+        <v>19.5</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -18765,27 +18765,27 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -18805,12 +18805,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -18830,12 +18830,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>San Mauro Marchesato</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>17.726</v>
+        <v>63.18</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -18866,27 +18866,27 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>VIA PAOLO EMILIO 10</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
@@ -18906,93 +18906,93 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>PV Altomonte e Castrovillari</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Altomonte</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J184" t="n">
-        <v>7</v>
+        <v>77.7</v>
       </c>
       <c r="K184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
@@ -19007,12 +19007,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -19022,36 +19022,36 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>San Mauro Marchesato</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J185" t="n">
-        <v>7.2</v>
+        <v>17.726</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -19068,27 +19068,27 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA PAOLO EMILIO 10</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
@@ -19108,37 +19108,37 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -19148,48 +19148,48 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J186" t="n">
-        <v>67.84</v>
+        <v>7</v>
       </c>
       <c r="K186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
@@ -19209,12 +19209,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -19224,7 +19224,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -19234,12 +19234,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -19249,11 +19249,11 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J187" t="n">
-        <v>40.31</v>
+        <v>7.2</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -19270,27 +19270,27 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -19310,12 +19310,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -19325,7 +19325,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -19335,12 +19335,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -19350,11 +19350,11 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J188" t="n">
-        <v>14.528</v>
+        <v>67.84</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -19371,17 +19371,17 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
@@ -19411,12 +19411,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Scaldasole 41</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Scaldasole</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -19455,7 +19455,7 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>37.16</v>
+        <v>40.31</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -19472,32 +19472,32 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
@@ -19512,12 +19512,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -19527,22 +19527,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>PV Alessandria</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -19556,7 +19556,7 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>5</v>
+        <v>14.528</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -19568,37 +19568,37 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>VIA CLAUDIO BEAUMONT 7</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
@@ -19613,12 +19613,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -19628,22 +19628,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>PV Tortona</t>
+          <t>Scaldasole 41</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Tortona</t>
+          <t>Scaldasole</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>10</v>
+        <v>37.16</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -19674,32 +19674,32 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>VIA CLAUDIO BEAUMONT 7</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
@@ -19714,12 +19714,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -19729,36 +19729,36 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PV Alessandria</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J192" t="n">
-        <v>48.5</v>
+        <v>5</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -19770,32 +19770,32 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -19815,12 +19815,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -19830,36 +19830,36 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>PV Tortona</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Tortona</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J193" t="n">
-        <v>73.7</v>
+        <v>10</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -19876,27 +19876,27 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
@@ -19916,12 +19916,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -19941,12 +19941,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -19960,7 +19960,7 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>84.3</v>
+        <v>48.5</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -19977,17 +19977,17 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -19997,7 +19997,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
@@ -20017,12 +20017,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -20032,7 +20032,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -20047,7 +20047,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -20061,7 +20061,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>36.32</v>
+        <v>73.7</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -20078,27 +20078,27 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
@@ -20118,12 +20118,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -20162,7 +20162,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>29.73</v>
+        <v>84.3</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -20189,7 +20189,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -20219,88 +20219,88 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>7</v>
+        <v>36.32</v>
       </c>
       <c r="K197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -20320,12 +20320,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -20335,36 +20335,36 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>72</v>
+        <v>29.73</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -20381,17 +20381,17 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -20421,12 +20421,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -20436,36 +20436,36 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>PV Villadose</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Villadose</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>19.88</v>
+        <v>37.481</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -20482,32 +20482,32 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
@@ -20522,88 +20522,88 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J200" t="n">
-        <v>19.96</v>
+        <v>7</v>
       </c>
       <c r="K200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -20623,12 +20623,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -20638,36 +20638,36 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J201" t="n">
-        <v>22.925</v>
+        <v>72</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -20684,27 +20684,27 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
@@ -20724,12 +20724,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -20768,7 +20768,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>19.968</v>
+        <v>19.88</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -20785,27 +20785,27 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
@@ -20825,12 +20825,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -20840,7 +20840,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -20886,27 +20886,27 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
@@ -20926,88 +20926,88 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
+          <t>Potenza</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Melfi</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Salerno</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>22.925</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>VIA LUIGI BUZZI 6</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>CASALE MONFERRATO</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>15033</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
           <t>Torino</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Pinerolo</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Nord Ovest</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="J204" t="n">
-        <v>12</v>
-      </c>
-      <c r="K204" t="n">
-        <v>1</v>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>Attivo</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>Costruzione</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>VIA MATTATOIO 3</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>SALUZZO</t>
-        </is>
-      </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>12037</t>
-        </is>
-      </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>Cuneo</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
@@ -21027,12 +21027,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -21042,36 +21042,36 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J205" t="n">
-        <v>46.7235</v>
+        <v>19.968</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -21088,17 +21088,17 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
@@ -21108,7 +21108,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
@@ -21128,12 +21128,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -21143,36 +21143,36 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J206" t="n">
-        <v>2</v>
+        <v>19.96</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -21189,27 +21189,27 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
@@ -21229,22 +21229,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -21273,44 +21273,44 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>18.774</v>
+        <v>12</v>
       </c>
       <c r="K207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -21330,22 +21330,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -21355,12 +21355,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -21374,10 +21374,10 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>18</v>
+        <v>46.7235</v>
       </c>
       <c r="K208" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -21386,32 +21386,32 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
@@ -21431,12 +21431,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -21446,36 +21446,36 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J209" t="n">
-        <v>96.09</v>
+        <v>2</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -21492,27 +21492,27 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
@@ -21532,12 +21532,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -21547,36 +21547,36 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J210" t="n">
-        <v>20.787</v>
+        <v>18.774</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -21593,27 +21593,27 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
@@ -21633,101 +21633,404 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>PV Maserano</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Biella</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Masserano</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>18</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>VIA VARALLO POMBIA 44</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>CASTELLETTO SOPRA TICINO</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>28053</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Maniago Solar 1- ELLO 11</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Friuli-Venezia Giulia</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Pordenone</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Maniago</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>BOLZANO</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>39100</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PV PORTOGRUARO</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Portogruaro</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>20.787</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U213" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t>EGPM-FV082</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E214" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>Latina</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>Pontinia</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
+      <c r="H214" t="inlineStr">
         <is>
           <t>Sud</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I214" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="J211" t="n">
+      <c r="J214" t="n">
         <v>18.419</v>
       </c>
-      <c r="K211" t="n">
+      <c r="K214" t="n">
         <v>0</v>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t>In pipeline</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t>Autorizzazioni</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr">
+      <c r="N214" t="inlineStr">
         <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O211" t="inlineStr">
+      <c r="O214" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P211" t="inlineStr">
+      <c r="P214" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q211" t="inlineStr">
+      <c r="Q214" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R211" t="inlineStr">
+      <c r="R214" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S211" t="inlineStr">
+      <c r="S214" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T211" t="inlineStr">
+      <c r="T214" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U211" t="n">
+      <c r="U214" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21742,7 +22045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U182"/>
+  <dimension ref="A1:U184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37203,12 +37506,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -37218,36 +37521,36 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>PV Lonato del Garda</t>
+          <t>PV Espe-1</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lonato del Garda</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>19.27</v>
+        <v>12</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -37259,32 +37562,32 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>VIA ARRIGO BOITO 8</t>
+          <t>VIA DELL'ARTIGIANATO 6</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>GRANTORTO</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>35010</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
@@ -37304,12 +37607,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -37319,36 +37622,36 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Lonato</t>
+          <t>PV Espe-2</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bedizzole</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>23.2</v>
+        <v>10</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -37360,32 +37663,32 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
+          <t>VIA DELL'ARTIGIANATO 6</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>GRANTORTO</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>35010</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -37405,12 +37708,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -37420,36 +37723,36 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Lonato del Garda</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Lonato del Garda</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>19.5</v>
+        <v>19.27</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -37466,27 +37769,27 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -37506,12 +37809,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -37521,36 +37824,36 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Lonato</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cassano all'Ionio</t>
+          <t>Bedizzole</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>63.18</v>
+        <v>23.2</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -37567,27 +37870,27 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -37607,12 +37910,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -37622,7 +37925,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>PV Altomonte e Castrovillari</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -37632,26 +37935,26 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Altomonte</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J158" t="n">
-        <v>77.7</v>
+        <v>19.5</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -37668,27 +37971,27 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
@@ -37708,12 +38011,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -37723,7 +38026,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -37733,12 +38036,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>San Mauro Marchesato</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -37752,7 +38055,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>17.726</v>
+        <v>63.18</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -37769,27 +38072,27 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>VIA PAOLO EMILIO 10</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -37809,12 +38112,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -37824,36 +38127,36 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>PV Altomonte e Castrovillari</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Altomonte</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>7.2</v>
+        <v>77.7</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -37870,7 +38173,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -37880,7 +38183,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -37890,7 +38193,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -37910,12 +38213,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -37925,36 +38228,36 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>San Mauro Marchesato</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>40.31</v>
+        <v>17.726</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -37971,7 +38274,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA PAOLO EMILIO 10</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -37981,7 +38284,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -38011,12 +38314,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -38026,22 +38329,22 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>PV Alessandria</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -38051,11 +38354,11 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -38067,32 +38370,32 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>VIA CLAUDIO BEAUMONT 7</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -38112,12 +38415,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -38127,22 +38430,22 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>PV Tortona</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tortona</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -38156,7 +38459,7 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>10</v>
+        <v>40.31</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -38173,27 +38476,27 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>VIA CLAUDIO BEAUMONT 7</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
@@ -38213,12 +38516,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -38228,36 +38531,36 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>PV Alessandria</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>48.5</v>
+        <v>5</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -38269,32 +38572,32 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -38314,12 +38617,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -38329,36 +38632,36 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>PV Tortona</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Tortona</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>73.7</v>
+        <v>10</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -38375,27 +38678,27 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
@@ -38415,12 +38718,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -38430,7 +38733,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -38440,12 +38743,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -38459,7 +38762,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>84.3</v>
+        <v>48.5</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -38476,17 +38779,17 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -38496,7 +38799,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -38516,12 +38819,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -38531,7 +38834,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -38546,7 +38849,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -38560,7 +38863,7 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>36.32</v>
+        <v>73.7</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -38577,27 +38880,27 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -38617,12 +38920,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -38632,7 +38935,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -38647,7 +38950,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -38661,7 +38964,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>29.73</v>
+        <v>84.3</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -38678,7 +38981,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -38688,7 +38991,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -38718,88 +39021,88 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>7</v>
+        <v>36.32</v>
       </c>
       <c r="K169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
@@ -38819,12 +39122,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -38834,36 +39137,36 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>72</v>
+        <v>29.73</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -38880,17 +39183,17 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -38900,7 +39203,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -38920,88 +39223,88 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>19.88</v>
+        <v>7</v>
       </c>
       <c r="K171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
@@ -39021,12 +39324,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -39036,36 +39339,36 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>19.96</v>
+        <v>72</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -39082,17 +39385,17 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
@@ -39102,7 +39405,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -39122,12 +39425,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -39137,7 +39440,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -39152,7 +39455,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -39166,7 +39469,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>22.925</v>
+        <v>19.88</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -39183,27 +39486,27 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -39223,12 +39526,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -39238,7 +39541,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -39253,7 +39556,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -39267,7 +39570,7 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>19.968</v>
+        <v>19.96</v>
       </c>
       <c r="K174" t="n">
         <v>0</v>
@@ -39284,17 +39587,17 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
@@ -39304,7 +39607,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
@@ -39324,12 +39627,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -39339,7 +39642,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -39354,7 +39657,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -39368,7 +39671,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>19.96</v>
+        <v>22.925</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -39385,27 +39688,27 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -39425,88 +39728,88 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>12</v>
+        <v>19.968</v>
       </c>
       <c r="K176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -39526,12 +39829,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -39541,36 +39844,36 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>46.7235</v>
+        <v>19.96</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -39587,27 +39890,27 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -39627,22 +39930,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -39671,34 +39974,34 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
@@ -39728,12 +40031,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -39743,7 +40046,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -39758,7 +40061,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -39772,7 +40075,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>18.774</v>
+        <v>46.7235</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -39789,7 +40092,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -39829,22 +40132,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -39854,12 +40157,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -39873,10 +40176,10 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K180" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -39885,32 +40188,32 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
@@ -39930,12 +40233,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -39945,36 +40248,36 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>96.09</v>
+        <v>18.774</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -39991,27 +40294,27 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -40031,101 +40334,303 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>PV Maserano</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Biella</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Masserano</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Nord Ovest</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>18</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>VIA VARALLO POMBIA 44</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>CASTELLETTO SOPRA TICINO</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>28053</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Maniago Solar 1- ELLO 11</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Friuli-Venezia Giulia</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Pordenone</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Maniago</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>BOLZANO</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>39100</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>BZ</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
           <t>FLYSUN 10 SRL</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>FLYSUN 10 SRL</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>PV PORTOGRUARO</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E184" t="inlineStr">
         <is>
           <t>Veneto</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>Venezia</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>Portogruaro</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="H184" t="inlineStr">
         <is>
           <t>Nord Est</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="I184" t="inlineStr">
         <is>
           <t>Venezia</t>
         </is>
       </c>
-      <c r="J182" t="n">
+      <c r="J184" t="n">
         <v>20.787</v>
       </c>
-      <c r="K182" t="n">
+      <c r="K184" t="n">
         <v>0</v>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t>In pipeline</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t>Autorizzazioni</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr">
+      <c r="N184" t="inlineStr">
         <is>
           <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
-      <c r="O182" t="inlineStr">
+      <c r="O184" t="inlineStr">
         <is>
           <t>TORINO</t>
         </is>
       </c>
-      <c r="P182" t="inlineStr">
+      <c r="P184" t="inlineStr">
         <is>
           <t>10153</t>
         </is>
       </c>
-      <c r="Q182" t="inlineStr">
+      <c r="Q184" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="R182" t="inlineStr">
+      <c r="R184" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="S182" t="inlineStr">
+      <c r="S184" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T182" t="inlineStr">
+      <c r="T184" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U182" t="n">
+      <c r="U184" t="n">
         <v>1</v>
       </c>
     </row>
@@ -40140,7 +40645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43077,12 +43582,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -43092,36 +43597,36 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>PV Villadose</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Villadose</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>18.419</v>
+        <v>37.481</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -43138,40 +43643,141 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
+          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>ROVIGO</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>45100</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>STESSA FILIALE</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -43186,7 +43792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44458,7 +45064,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -44470,7 +45076,7 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>36.32</v>
+        <v>37.481</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -44479,19 +45085,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>34.776</v>
+        <v>36.32</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -44500,7 +45106,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -44512,7 +45118,7 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>34.6</v>
+        <v>34.776</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -44521,7 +45127,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -44533,7 +45139,7 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>33.972</v>
+        <v>34.6</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -44542,19 +45148,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>33.527</v>
+        <v>33.972</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -44563,19 +45169,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>31.4</v>
+        <v>33.527</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -44584,61 +45190,61 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>30.148</v>
+        <v>31.4</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>28.38</v>
+        <v>30.148</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>28.3</v>
+        <v>28.38</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -44647,61 +45253,61 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>28.209</v>
+        <v>28.3</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>27.136</v>
+        <v>28.209</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>26.95</v>
+        <v>27.136</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -44715,14 +45321,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>25.3</v>
+        <v>26.95</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
@@ -44731,19 +45337,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>25.29</v>
+        <v>25.3</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -44752,19 +45358,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>24.95</v>
+        <v>25.29</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -44773,7 +45379,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -44782,52 +45388,52 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>24.77</v>
+        <v>24.95</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
         <v>24.77</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>24</v>
+        <v>24.77</v>
       </c>
       <c r="E78" t="n">
         <v>1</v>
@@ -44836,19 +45442,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
@@ -44857,19 +45463,19 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>22.925</v>
+        <v>23.2</v>
       </c>
       <c r="E80" t="n">
         <v>1</v>
@@ -44878,19 +45484,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>22.57</v>
+        <v>22.925</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -44899,19 +45505,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>20.787</v>
+        <v>22.57</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -44920,7 +45526,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -44932,28 +45538,28 @@
         <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>19.968</v>
+        <v>20.787</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -44962,40 +45568,40 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>19.96</v>
+        <v>20</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>19.5</v>
+        <v>19.968</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -45009,14 +45615,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>19.27</v>
+        <v>19.96</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -45025,19 +45631,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>19.021</v>
+        <v>19.5</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -45046,19 +45652,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>18.419</v>
+        <v>19.27</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -45067,19 +45673,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>18</v>
+        <v>19.021</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -45088,19 +45694,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>17.8</v>
+        <v>18.419</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
@@ -45109,19 +45715,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>17.726</v>
+        <v>18</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -45130,19 +45736,19 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>16.63</v>
+        <v>17.8</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -45151,19 +45757,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>15</v>
+        <v>17.726</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -45172,7 +45778,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -45184,7 +45790,7 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>14.03</v>
+        <v>16.63</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -45193,40 +45799,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>13.56</v>
+        <v>14.03</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -45235,40 +45841,40 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Bari</t>
-        </is>
-      </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>11.45</v>
+        <v>13.56</v>
       </c>
       <c r="E99" t="n">
         <v>1</v>
@@ -45277,19 +45883,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="E100" t="n">
         <v>1</v>
@@ -45298,19 +45904,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>8.984</v>
+        <v>11.45</v>
       </c>
       <c r="E101" t="n">
         <v>1</v>
@@ -45319,19 +45925,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -45340,19 +45946,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>7.02</v>
+        <v>8.984</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
@@ -45361,19 +45967,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
@@ -45382,19 +45988,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
@@ -45403,19 +46009,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -45424,40 +46030,40 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="E107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -45466,40 +46072,40 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>0.93</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
@@ -45508,19 +46114,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
         <v>1</v>
@@ -45529,21 +46135,63 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>Bergamo</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Livorno</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
         <is>
           <t>Lucca</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>1</v>
-      </c>
-      <c r="D112" t="n">
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
         <v>0.5</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>1</v>
       </c>
     </row>
@@ -45580,7 +46228,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3">
@@ -45590,7 +46238,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8944.3475</v>
+        <v>9003.8285</v>
       </c>
     </row>
     <row r="4">
@@ -45600,7 +46248,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -45610,7 +46258,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -45825,43 +46473,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>224.8</v>
+        <v>261.531</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>224.05</v>
+        <v>224.8</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -45930,43 +46578,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>177.86</v>
+        <v>190.177</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>168.177</v>
+        <v>177.86</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -46862,7 +47510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47286,7 +47934,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -47296,13 +47944,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>33.527</v>
+        <v>37.481</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -47312,13 +47960,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>31.4</v>
+        <v>33.527</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -47328,13 +47976,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>31.26</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>BT</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -47344,13 +47992,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>28.1</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -47360,13 +48008,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>22.925</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -47376,13 +48024,13 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>22.57</v>
+        <v>22.925</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -47392,29 +48040,29 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>18.419</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -47424,13 +48072,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>16.63</v>
+        <v>18.419</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -47440,13 +48088,13 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>8.984</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AN</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -47456,22 +48104,54 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0.93</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>8.984</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>LI</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U214"/>
+  <dimension ref="A1:U215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21835,12 +21835,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -21850,22 +21850,22 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>GREENFRUT</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Bicinicco</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -21875,11 +21875,11 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J213" t="n">
-        <v>20.787</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -21896,32 +21896,32 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>BICINICCO</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>33050</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
@@ -21936,12 +21936,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -21951,36 +21951,36 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J214" t="n">
-        <v>18.419</v>
+        <v>20.787</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -21997,40 +21997,141 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr">
+      <c r="O215" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P214" t="inlineStr">
+      <c r="P215" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q214" t="inlineStr">
+      <c r="Q215" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R214" t="inlineStr">
+      <c r="R215" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S214" t="inlineStr">
+      <c r="S215" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T214" t="inlineStr">
+      <c r="T215" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U214" t="n">
+      <c r="U215" t="n">
         <v>1</v>
       </c>
     </row>
@@ -40645,7 +40746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43683,12 +43784,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -43698,36 +43799,36 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>GREENFRUT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Bicinicco</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>18.419</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -43744,40 +43845,141 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
+          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>BICINICCO</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>33050</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>UD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>STESSA FILIALE</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U31" t="n">
+      <c r="U32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -43792,7 +43994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44539,43 +44741,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>68.09699999999999</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>67.84</v>
+        <v>68.09699999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -44586,14 +44788,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>67</v>
+        <v>67.84</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -44602,40 +44804,40 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>65.91200000000001</v>
+        <v>67</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>65.4975</v>
+        <v>65.91200000000001</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -44644,40 +44846,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>64.7</v>
+        <v>65.4975</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>64.67400000000001</v>
+        <v>64.7</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -44686,61 +44888,61 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>62.22</v>
+        <v>64.67400000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>60.05</v>
+        <v>62.22</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>56.54</v>
+        <v>60.05</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -44749,19 +44951,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>55.55</v>
+        <v>56.54</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -44770,103 +44972,103 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>53.3</v>
+        <v>55.55</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>51.807</v>
+        <v>53.3</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>51.688</v>
+        <v>51.807</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>51.3</v>
+        <v>51.688</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -44875,19 +45077,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>47.9</v>
+        <v>50.6</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -44896,19 +45098,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>47.47</v>
+        <v>47.9</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -44922,14 +45124,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>44.036</v>
+        <v>47.47</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -44938,19 +45140,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>43.65</v>
+        <v>44.036</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -44959,61 +45161,61 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>41.875</v>
+        <v>43.65</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>41.758</v>
+        <v>41.875</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>40.31</v>
+        <v>41.758</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -45022,40 +45224,40 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>40.287</v>
+        <v>40.31</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>39.84</v>
+        <v>40.287</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
@@ -45064,28 +45266,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>37.481</v>
+        <v>39.84</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -45097,7 +45299,7 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>36.32</v>
+        <v>37.481</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -45106,19 +45308,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>34.776</v>
+        <v>36.32</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -45127,7 +45329,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -45139,7 +45341,7 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>34.6</v>
+        <v>34.776</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -45148,7 +45350,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -45160,7 +45362,7 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>33.972</v>
+        <v>34.6</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -45169,19 +45371,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>33.527</v>
+        <v>33.972</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -45190,19 +45392,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>31.4</v>
+        <v>33.527</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -45211,61 +45413,61 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>30.148</v>
+        <v>31.4</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>28.38</v>
+        <v>30.148</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>28.3</v>
+        <v>28.38</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -45274,61 +45476,61 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>28.209</v>
+        <v>28.3</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>27.136</v>
+        <v>28.209</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>26.95</v>
+        <v>27.136</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
@@ -45342,14 +45544,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>25.3</v>
+        <v>26.95</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -45358,19 +45560,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>25.29</v>
+        <v>25.3</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -45379,19 +45581,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>24.95</v>
+        <v>25.29</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -45400,7 +45602,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -45409,52 +45611,52 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>24.77</v>
+        <v>24.95</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
         <v>24.77</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>24</v>
+        <v>24.77</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
@@ -45463,19 +45665,19 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="E80" t="n">
         <v>1</v>
@@ -45484,19 +45686,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>22.925</v>
+        <v>23.2</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -45505,19 +45707,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>22.57</v>
+        <v>22.925</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -45526,19 +45728,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>22</v>
+        <v>22.57</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -45547,19 +45749,19 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>20.787</v>
+        <v>22</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -45568,49 +45770,49 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>20</v>
+        <v>20.787</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>19.968</v>
+        <v>20</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -45622,7 +45824,7 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -45631,19 +45833,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>19.5</v>
+        <v>19.96</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -45652,19 +45854,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>19.27</v>
+        <v>19.5</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -45673,19 +45875,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>19.021</v>
+        <v>19.27</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -45694,19 +45896,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>18.419</v>
+        <v>19.021</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
@@ -45715,19 +45917,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>18</v>
+        <v>18.419</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -45736,19 +45938,19 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -45757,19 +45959,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>17.726</v>
+        <v>17.8</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -45778,19 +45980,19 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>16.63</v>
+        <v>17.726</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -45799,19 +46001,19 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>15</v>
+        <v>16.63</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
@@ -45820,19 +46022,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>14.03</v>
+        <v>15</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -45841,61 +46043,61 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>13.56</v>
+        <v>14</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>12</v>
+        <v>13.56</v>
       </c>
       <c r="E100" t="n">
         <v>1</v>
@@ -45904,19 +46106,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>11.45</v>
+        <v>12</v>
       </c>
       <c r="E101" t="n">
         <v>1</v>
@@ -45925,7 +46127,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -45937,7 +46139,7 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>9.199999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -45946,19 +46148,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>8.984</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
@@ -45967,19 +46169,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>7.2</v>
+        <v>8.984</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
@@ -45988,19 +46190,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>7.02</v>
+        <v>7.2</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
@@ -46009,19 +46211,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -46035,7 +46237,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -46051,19 +46253,19 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -46072,43 +46274,43 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -46119,14 +46321,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E111" t="n">
         <v>1</v>
@@ -46135,19 +46337,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C112" t="n">
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>0.93</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -46156,19 +46358,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -46182,7 +46384,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -46192,6 +46394,27 @@
         <v>0.5</v>
       </c>
       <c r="E114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Lucca</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E115" t="n">
         <v>1</v>
       </c>
     </row>
@@ -46228,7 +46451,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
@@ -46238,7 +46461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9003.8285</v>
+        <v>9072.3385</v>
       </c>
     </row>
     <row r="4">
@@ -46248,7 +46471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -46272,7 +46495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47040,19 +47263,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>67.84</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -47061,40 +47284,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>67.048</v>
+        <v>67.84</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>64.8</v>
+        <v>67.048</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -47103,61 +47326,61 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>60.95</v>
+        <v>64.8</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>60</v>
+        <v>60.95</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>48.5</v>
+        <v>60</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -47166,124 +47389,124 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>42.47</v>
+        <v>48.5</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>38.754</v>
+        <v>42.47</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>38.535</v>
+        <v>38.754</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>38.16</v>
+        <v>38.535</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>37.226</v>
+        <v>38.16</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>37.2</v>
+        <v>37.226</v>
       </c>
       <c r="E48" t="n">
         <v>2</v>
@@ -47292,124 +47515,124 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pesaro e Urbino</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>28.38</v>
+        <v>37.2</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Pesaro e Urbino</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>24.82</v>
+        <v>28.38</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>20.787</v>
+        <v>24.82</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>19.995</v>
+        <v>20.787</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>18</v>
+        <v>19.995</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Rieti</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -47418,19 +47641,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Rieti</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -47439,63 +47662,84 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>7.2</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Monza e della Brianza</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Lombardia</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Piacenza</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="n">
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
         <v>7</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -47510,7 +47754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47854,7 +48098,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -47864,13 +48108,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>64.90000000000001</v>
+        <v>68.51000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PZ</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -47880,13 +48124,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>60.05</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>PZ</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -47896,13 +48140,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>56.54</v>
+        <v>60.05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -47912,13 +48156,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>50.96</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -47928,13 +48172,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>40.2</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -47944,13 +48188,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>37.481</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -47960,13 +48204,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>33.527</v>
+        <v>37.481</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -47976,13 +48220,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>31.4</v>
+        <v>33.527</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -47992,13 +48236,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>31.26</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>BT</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -48008,13 +48252,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>28.1</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -48024,13 +48268,13 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>22.925</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -48040,45 +48284,45 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>22.57</v>
+        <v>22.925</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>22</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>18.419</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -48088,13 +48332,13 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>18</v>
+        <v>18.419</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -48104,13 +48348,13 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>16.63</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -48120,13 +48364,13 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>8.984</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AN</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -48136,22 +48380,38 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0.93</v>
+        <v>8.984</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>AN</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>LI</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -21269,7 +21269,7 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>121697</v>
+        <v>121.697</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -41586,7 +41586,7 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>121697</v>
+        <v>121.697</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -47251,28 +47251,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>121697</v>
+        <v>828.9549999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -47281,61 +47281,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>828.9549999999999</v>
+        <v>701.95</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>701.95</v>
+        <v>598.95</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Bari</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bari</t>
-        </is>
-      </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>598.95</v>
+        <v>484.557</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -47344,40 +47344,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>484.557</v>
+        <v>430.122</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>430.122</v>
+        <v>354.3</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -47386,40 +47386,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>354.3</v>
+        <v>328.8</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Catania</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Catania</t>
-        </is>
-      </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>328.8</v>
+        <v>250</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -47428,31 +47428,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>220.6</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>220.6</v>
+        <v>161.868</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -47466,101 +47466,101 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>161.868</v>
+        <v>144.335</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>144.335</v>
+        <v>141.747</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>141.747</v>
+        <v>141.56</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>141.56</v>
+        <v>140.88</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>140.88</v>
+        <v>140.413</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -47571,101 +47571,101 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>140.413</v>
+        <v>137.23</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>137.23</v>
+        <v>130.151</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>130.151</v>
+        <v>128</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>128</v>
+        <v>124.56</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>124.56</v>
+        <v>121.697</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -49790,7 +49790,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>131361.8885</v>
+        <v>9786.585500000001</v>
       </c>
     </row>
     <row r="4">
@@ -49857,28 +49857,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>121867.461</v>
+        <v>787.7629999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -49887,19 +49887,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>787.7629999999999</v>
+        <v>752.27</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -49908,40 +49908,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>752.27</v>
+        <v>737.7</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>737.7</v>
+        <v>728.295</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Brindisi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -49950,19 +49950,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>728.295</v>
+        <v>564.484</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brindisi</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -49971,55 +49971,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>564.484</v>
+        <v>423.438</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Trapani</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>423.438</v>
+        <v>330.18</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trapani</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>330.18</v>
+        <v>292.158</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -51437,7 +51437,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -51447,13 +51447,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>121697</v>
+        <v>141.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -51463,7 +51463,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>141.56</v>
+        <v>121.697</v>
       </c>
     </row>
     <row r="22">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U244"/>
+  <dimension ref="A1:U245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20518,12 +20518,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -20533,36 +20533,36 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>PV Lonato del Garda</t>
+          <t>Cuniola</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lonato del Garda</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J200" t="n">
-        <v>19.27</v>
+        <v>56.07</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>VIA ARRIGO BOITO 8</t>
+          <t>LARGO ARTURO TOSCANINI 1</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -20619,12 +20619,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Lonato</t>
+          <t>PV Lonato del Garda</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bedizzole</t>
+          <t>Lonato del Garda</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -20663,7 +20663,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>23.2</v>
+        <v>19.27</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -20680,27 +20680,27 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
@@ -20720,12 +20720,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>PV Bedizzole</t>
+          <t>Lonato</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>16.2</v>
+        <v>23.2</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -20781,27 +20781,27 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>VIA DELL'UNIONE 1</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
@@ -20821,12 +20821,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -20836,36 +20836,36 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Bedizzole</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Bedizzole</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J203" t="n">
-        <v>19.5</v>
+        <v>16.2</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -20882,27 +20882,27 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA DELL'UNIONE 1</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
@@ -20922,12 +20922,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -20947,26 +20947,26 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J204" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -20983,27 +20983,27 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
@@ -21023,12 +21023,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>PV Altomonte e Castrovillari</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Altomonte</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -21067,7 +21067,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>77.7</v>
+        <v>63.18</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -21124,12 +21124,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -21139,7 +21139,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>PV Altomonte e Castrovillari</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -21149,12 +21149,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>San Mauro Marchesato</t>
+          <t>Altomonte</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -21168,7 +21168,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>17.726</v>
+        <v>77.7</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -21185,27 +21185,27 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>VIA PAOLO EMILIO 10</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
@@ -21225,68 +21225,68 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>San Mauro Marchesato</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J207" t="n">
-        <v>7</v>
+        <v>17.726</v>
       </c>
       <c r="K207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA PAOLO EMILIO 10</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -21296,7 +21296,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
@@ -21306,12 +21306,12 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
@@ -21326,37 +21326,37 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -21366,53 +21366,53 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J208" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
@@ -21427,12 +21427,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -21452,12 +21452,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -21467,11 +21467,11 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J209" t="n">
-        <v>67.84</v>
+        <v>7.2</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -21508,12 +21508,12 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
@@ -21528,12 +21528,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -21553,12 +21553,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -21568,11 +21568,11 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J210" t="n">
-        <v>40.31</v>
+        <v>67.84</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -21589,32 +21589,32 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
@@ -21629,12 +21629,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -21659,7 +21659,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>14.528</v>
+        <v>40.31</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -21690,32 +21690,32 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
@@ -21730,12 +21730,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Scaldasole 41</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -21760,7 +21760,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Scaldasole</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -21774,7 +21774,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>37.16</v>
+        <v>14.528</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -21791,17 +21791,17 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -21831,12 +21831,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -21846,22 +21846,22 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PV Alessandria</t>
+          <t>Scaldasole 41</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Scaldasole</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>5</v>
+        <v>37.16</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -21887,37 +21887,37 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>VIA CLAUDIO BEAUMONT 7</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
@@ -21947,7 +21947,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>PV Tortona</t>
+          <t>PV Alessandria</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -21962,7 +21962,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Tortona</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -21976,7 +21976,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -21988,7 +21988,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -22033,12 +22033,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -22048,22 +22048,22 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>PV Bissina</t>
+          <t>PV Tortona</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Santa Cristina e Bissone</t>
+          <t>Tortona</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -22077,7 +22077,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>78.46299999999999</v>
+        <v>10</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -22094,32 +22094,32 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
@@ -22134,12 +22134,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Cascina Grande</t>
+          <t>PV Bissina</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -22164,7 +22164,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dorno</t>
+          <t>Santa Cristina e Bissone</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -22178,7 +22178,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>121.697</v>
+        <v>78.46299999999999</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -22195,32 +22195,32 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>VIA GIOSUE' CARDUCCI 8</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>TRIESTE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
@@ -22235,12 +22235,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -22250,36 +22250,36 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>Cascina Grande</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Dorno</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J217" t="n">
-        <v>48.5</v>
+        <v>121.697</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -22296,27 +22296,27 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA GIOSUE' CARDUCCI 8</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TRIESTE</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -22351,7 +22351,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -22361,12 +22361,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -22437,12 +22437,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -22481,7 +22481,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -22498,17 +22498,17 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -22518,7 +22518,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
@@ -22538,12 +22538,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -22582,7 +22582,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>36.32</v>
+        <v>84.3</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -22599,27 +22599,27 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
@@ -22639,12 +22639,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -22654,7 +22654,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -22669,7 +22669,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -22683,7 +22683,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>29.73</v>
+        <v>36.32</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -22700,27 +22700,27 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
@@ -22740,12 +22740,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -22755,7 +22755,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>PV Villadose</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Villadose</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>37.481</v>
+        <v>29.73</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -22801,32 +22801,32 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>ROVIGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
@@ -22841,12 +22841,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>CASTELNOVO B.</t>
+          <t>PV Villadose</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -22871,7 +22871,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Castelnovo Bariano</t>
+          <t>Villadose</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -22885,7 +22885,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>15.03</v>
+        <v>37.481</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -22902,32 +22902,32 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>VIA VARESE 194</t>
+          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
@@ -22942,12 +22942,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Bagnoli 1, 2, 3, 4</t>
+          <t>CASTELNOVO B.</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -22967,26 +22967,26 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
+          <t>Rovigo</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Castelnovo Bariano</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
           <t>Padova</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Bagnoli di Sopra</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Nord Est</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>Padova</t>
-        </is>
-      </c>
       <c r="J224" t="n">
-        <v>26.67</v>
+        <v>15.03</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>VIA VARESE 194</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -23013,7 +23013,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -23023,7 +23023,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
@@ -23043,12 +23043,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>PV via Murazze snc</t>
+          <t>Bagnoli 1, 2, 3, 4</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -23068,12 +23068,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Porto Viro</t>
+          <t>Bagnoli di Sopra</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -23087,7 +23087,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>19.56</v>
+        <v>26.67</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -23144,88 +23144,88 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV via Murazze snc</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Porto Viro</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J226" t="n">
-        <v>7</v>
+        <v>19.56</v>
       </c>
       <c r="K226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
@@ -23245,22 +23245,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -23270,63 +23270,63 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J227" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
@@ -23346,12 +23346,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>FABBRICO</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -23371,12 +23371,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Reggio nell'Emilia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Fabbrico</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -23390,7 +23390,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>16.806</v>
+        <v>72</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -23407,27 +23407,27 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>VIA ANTONIO ANDREUZZI 12</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
@@ -23447,12 +23447,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -23462,36 +23462,36 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>FABBRICO</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Fabbrico</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J229" t="n">
-        <v>19.88</v>
+        <v>16.806</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -23508,27 +23508,27 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA ANTONIO ANDREUZZI 12</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
@@ -23548,12 +23548,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -23609,27 +23609,27 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
@@ -23649,12 +23649,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -23664,7 +23664,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -23693,7 +23693,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -23710,27 +23710,27 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -23750,12 +23750,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -23765,7 +23765,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -23780,7 +23780,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -23794,7 +23794,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>19.968</v>
+        <v>22.925</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -23811,27 +23811,27 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
@@ -23851,12 +23851,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -23866,7 +23866,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -23881,7 +23881,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -23895,7 +23895,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -23912,27 +23912,27 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
@@ -23952,88 +23952,88 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J234" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
@@ -24053,22 +24053,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -24097,44 +24097,44 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
@@ -24154,12 +24154,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -24184,7 +24184,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -24198,7 +24198,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -24215,27 +24215,27 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
@@ -24255,12 +24255,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -24270,7 +24270,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -24299,7 +24299,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -24316,27 +24316,27 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
@@ -24356,22 +24356,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -24381,12 +24381,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -24400,10 +24400,10 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>18</v>
+        <v>18.774</v>
       </c>
       <c r="K238" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -24412,32 +24412,32 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
@@ -24457,54 +24457,54 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J239" t="n">
-        <v>96.09</v>
+        <v>18</v>
       </c>
       <c r="K239" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -24513,32 +24513,32 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
@@ -24558,12 +24558,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -24573,7 +24573,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>GREENFRUT</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -24583,26 +24583,26 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
+          <t>Pordenone</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Maniago</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
           <t>Udine</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>Bicinicco</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Nord Est</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>Udine</t>
-        </is>
-      </c>
       <c r="J240" t="n">
-        <v>68.51000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -24619,32 +24619,32 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>BICINICCO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T240" t="inlineStr">
@@ -24659,12 +24659,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -24674,22 +24674,22 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>GREENFRUT</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Bicinicco</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -24699,11 +24699,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J241" t="n">
-        <v>20.787</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -24720,32 +24720,32 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>BICINICCO</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>33050</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
@@ -24760,12 +24760,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Cona 1/2/3/4/5</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Cona</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -24804,7 +24804,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>27.867</v>
+        <v>20.787</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -24821,27 +24821,27 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
@@ -24861,12 +24861,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -24876,36 +24876,36 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>Cona 1/2/3/4/5</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Cona</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J243" t="n">
-        <v>18.419</v>
+        <v>27.867</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -24922,32 +24922,32 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>VIA ALDO MORO 233</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>FROSINONE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
@@ -24962,12 +24962,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -24977,7 +24977,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Latina Fondazione</t>
+          <t>EGPM-FV082</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -24992,7 +24992,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pontinia</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>28.61</v>
+        <v>18.419</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -25023,40 +25023,141 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
+          <t>VIA ALDO MORO 233</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>FROSINONE</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>STESSA FILIALE</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Latina Fondazione</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
           <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
-      <c r="O244" t="inlineStr">
+      <c r="O245" t="inlineStr">
         <is>
           <t>MILANO</t>
         </is>
       </c>
-      <c r="P244" t="inlineStr">
+      <c r="P245" t="inlineStr">
         <is>
           <t>20121</t>
         </is>
       </c>
-      <c r="Q244" t="inlineStr">
+      <c r="Q245" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="R244" t="inlineStr">
+      <c r="R245" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="S244" t="inlineStr">
+      <c r="S245" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T244" t="inlineStr">
+      <c r="T245" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U244" t="n">
+      <c r="U245" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25071,7 +25172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U210"/>
+  <dimension ref="A1:U211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42552,12 +42653,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -42567,36 +42668,36 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>PV Lonato del Garda</t>
+          <t>Cuniola</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lonato del Garda</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J174" t="n">
-        <v>19.27</v>
+        <v>56.07</v>
       </c>
       <c r="K174" t="n">
         <v>0</v>
@@ -42613,7 +42714,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>VIA ARRIGO BOITO 8</t>
+          <t>LARGO ARTURO TOSCANINI 1</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -42623,7 +42724,7 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
@@ -42653,12 +42754,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -42668,7 +42769,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Lonato</t>
+          <t>PV Lonato del Garda</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -42683,7 +42784,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bedizzole</t>
+          <t>Lonato del Garda</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -42697,7 +42798,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>23.2</v>
+        <v>19.27</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -42714,27 +42815,27 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
+          <t>VIA ARRIGO BOITO 8</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -42754,12 +42855,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -42769,7 +42870,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>PV Bedizzole</t>
+          <t>Lonato</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -42798,7 +42899,7 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>16.2</v>
+        <v>23.2</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
@@ -42815,27 +42916,27 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>VIA DELL'UNIONE 1</t>
+          <t>PIAZZA WALTHER VON DER VOGELWEIDE 8</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -42855,12 +42956,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -42870,36 +42971,36 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Canalicchi</t>
+          <t>PV Bedizzole</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Bedizzole</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>19.5</v>
+        <v>16.2</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -42916,27 +43017,27 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>VIA GIACOMO MATTEOTTI 31/2</t>
+          <t>VIA DELL'UNIONE 1</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -42956,12 +43057,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -42971,7 +43072,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Fattoria Solare San Biagio</t>
+          <t>Canalicchi</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -42981,26 +43082,26 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
           <t>Cosenza</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Cassano all'Ionio</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Cosenza</t>
-        </is>
-      </c>
       <c r="J178" t="n">
-        <v>63.18</v>
+        <v>19.5</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -43017,27 +43118,27 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIA GIACOMO MATTEOTTI 31/2</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
@@ -43057,12 +43158,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -43072,7 +43173,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>PV Altomonte e Castrovillari</t>
+          <t>Fattoria Solare San Biagio</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -43087,7 +43188,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Altomonte</t>
+          <t>Cassano all'Ionio</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -43101,7 +43202,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>77.7</v>
+        <v>63.18</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -43158,12 +43259,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -43173,7 +43274,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>PV Altomonte e Castrovillari</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -43183,12 +43284,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>San Mauro Marchesato</t>
+          <t>Altomonte</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -43202,7 +43303,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>17.726</v>
+        <v>77.7</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -43219,27 +43320,27 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>VIA PAOLO EMILIO 10</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
@@ -43259,12 +43360,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -43274,36 +43375,36 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>San Mauro Marchesato</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>7.2</v>
+        <v>17.726</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -43320,27 +43421,27 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA PAOLO EMILIO 10</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -43360,12 +43461,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -43375,7 +43476,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -43385,12 +43486,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -43400,11 +43501,11 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J182" t="n">
-        <v>40.31</v>
+        <v>7.2</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -43421,27 +43522,27 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -43461,12 +43562,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -43476,22 +43577,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PV Alessandria</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -43505,7 +43606,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>5</v>
+        <v>40.31</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -43517,32 +43618,32 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>VIA CLAUDIO BEAUMONT 7</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
@@ -43577,7 +43678,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>PV Tortona</t>
+          <t>PV Alessandria</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -43592,7 +43693,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Tortona</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -43606,7 +43707,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -43618,7 +43719,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -43663,12 +43764,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -43678,22 +43779,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Cascina Grande</t>
+          <t>PV Tortona</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dorno</t>
+          <t>Tortona</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -43707,7 +43808,7 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>121.697</v>
+        <v>10</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -43724,27 +43825,27 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>VIA GIOSUE' CARDUCCI 8</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>TRIESTE</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
@@ -43764,12 +43865,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -43779,36 +43880,36 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>Cascina Grande</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Dorno</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J186" t="n">
-        <v>48.5</v>
+        <v>121.697</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -43825,27 +43926,27 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA GIOSUE' CARDUCCI 8</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TRIESTE</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
@@ -43880,7 +43981,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -43890,12 +43991,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -43909,7 +44010,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -43966,12 +44067,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -43981,7 +44082,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -43996,7 +44097,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -44010,7 +44111,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -44027,17 +44128,17 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -44047,7 +44148,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
@@ -44067,12 +44168,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -44082,7 +44183,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -44097,7 +44198,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -44111,7 +44212,7 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>36.32</v>
+        <v>84.3</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -44128,27 +44229,27 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
@@ -44168,12 +44269,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -44183,7 +44284,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -44198,7 +44299,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -44212,7 +44313,7 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>29.73</v>
+        <v>36.32</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -44229,27 +44330,27 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
@@ -44269,12 +44370,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -44284,7 +44385,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>CASTELNOVO B.</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -44299,7 +44400,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Castelnovo Bariano</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -44313,7 +44414,7 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>15.03</v>
+        <v>29.73</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -44330,7 +44431,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>VIA VARESE 194</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -44340,7 +44441,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -44350,7 +44451,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
@@ -44370,12 +44471,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -44385,7 +44486,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Bagnoli 1, 2, 3, 4</t>
+          <t>CASTELNOVO B.</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -44395,26 +44496,26 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
+          <t>Rovigo</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Castelnovo Bariano</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
           <t>Padova</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Bagnoli di Sopra</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Nord Est</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Padova</t>
-        </is>
-      </c>
       <c r="J192" t="n">
-        <v>26.67</v>
+        <v>15.03</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -44431,7 +44532,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>VIA VARESE 194</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -44441,7 +44542,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -44451,7 +44552,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -44471,12 +44572,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -44486,7 +44587,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>PV via Murazze snc</t>
+          <t>Bagnoli 1, 2, 3, 4</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -44496,12 +44597,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Porto Viro</t>
+          <t>Bagnoli di Sopra</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -44515,7 +44616,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>19.56</v>
+        <v>26.67</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -44572,88 +44673,88 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV via Murazze snc</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Porto Viro</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>7</v>
+        <v>19.56</v>
       </c>
       <c r="K194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
@@ -44673,22 +44774,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -44698,63 +44799,63 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J195" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
@@ -44774,12 +44875,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -44789,7 +44890,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>FABBRICO</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -44799,12 +44900,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Reggio nell'Emilia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Fabbrico</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -44818,7 +44919,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>16.806</v>
+        <v>72</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -44835,27 +44936,27 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>VIA ANTONIO ANDREUZZI 12</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
@@ -44875,12 +44976,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -44890,36 +44991,36 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>FABBRICO</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Fabbrico</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>19.88</v>
+        <v>16.806</v>
       </c>
       <c r="K197" t="n">
         <v>0</v>
@@ -44936,27 +45037,27 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA ANTONIO ANDREUZZI 12</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -44976,12 +45077,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -44991,7 +45092,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -45020,7 +45121,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -45037,27 +45138,27 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -45077,12 +45178,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -45092,7 +45193,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -45107,7 +45208,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -45121,7 +45222,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -45138,27 +45239,27 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
@@ -45178,12 +45279,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -45193,7 +45294,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -45208,7 +45309,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -45222,7 +45323,7 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>19.968</v>
+        <v>22.925</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -45239,27 +45340,27 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -45279,12 +45380,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -45294,7 +45395,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -45309,7 +45410,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -45323,7 +45424,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -45340,27 +45441,27 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
@@ -45380,88 +45481,88 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J202" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
@@ -45481,22 +45582,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -45511,7 +45612,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -45525,44 +45626,44 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
@@ -45582,12 +45683,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -45597,7 +45698,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -45612,7 +45713,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -45626,7 +45727,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -45643,27 +45744,27 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
@@ -45683,12 +45784,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -45698,7 +45799,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -45713,7 +45814,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -45727,7 +45828,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -45744,27 +45845,27 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
@@ -45784,22 +45885,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -45809,12 +45910,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -45828,10 +45929,10 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>18</v>
+        <v>18.774</v>
       </c>
       <c r="K206" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -45840,32 +45941,32 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
@@ -45885,54 +45986,54 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J207" t="n">
-        <v>96.09</v>
+        <v>18</v>
       </c>
       <c r="K207" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -45941,32 +46042,32 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -45986,12 +46087,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -46001,22 +46102,22 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Maniago</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -46026,11 +46127,11 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J208" t="n">
-        <v>20.787</v>
+        <v>96.09</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -46047,27 +46148,27 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
@@ -46087,12 +46188,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -46102,7 +46203,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Cona 1/2/3/4/5</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -46117,7 +46218,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Cona</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -46131,7 +46232,7 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>27.867</v>
+        <v>20.787</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -46148,27 +46249,27 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
@@ -46188,12 +46289,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -46203,36 +46304,36 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Latina Fondazione</t>
+          <t>Cona 1/2/3/4/5</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Cona</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J210" t="n">
-        <v>28.61</v>
+        <v>27.867</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -46249,40 +46350,141 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
+          <t>VIA BIGLI 2</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U210" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Latina Fondazione</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
           <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
-      <c r="O210" t="inlineStr">
+      <c r="O211" t="inlineStr">
         <is>
           <t>MILANO</t>
         </is>
       </c>
-      <c r="P210" t="inlineStr">
+      <c r="P211" t="inlineStr">
         <is>
           <t>20121</t>
         </is>
       </c>
-      <c r="Q210" t="inlineStr">
+      <c r="Q211" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="R210" t="inlineStr">
+      <c r="R211" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="S210" t="inlineStr">
+      <c r="S211" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T210" t="inlineStr">
+      <c r="T211" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U210" t="n">
+      <c r="U211" t="n">
         <v>1</v>
       </c>
     </row>
@@ -50402,124 +50604,124 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>96.09</v>
+        <v>96.357</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>94.29499999999999</v>
+        <v>96.09</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>88.39</v>
+        <v>94.29499999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>86.68000000000001</v>
+        <v>88.39</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>86.2</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>83.3</v>
+        <v>86.2</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -50528,61 +50730,61 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bergamo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>81.375</v>
+        <v>83.3</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>77.98999999999999</v>
+        <v>81.375</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>75</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -50591,19 +50793,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -50612,19 +50814,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>71.31999999999999</v>
+        <v>72</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -50633,40 +50835,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>71.22999999999999</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>69.97999999999999</v>
+        <v>71.22999999999999</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -50675,40 +50877,40 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>68.51000000000001</v>
+        <v>69.97999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>67.84</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -50722,14 +50924,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>67</v>
+        <v>67.84</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -50738,40 +50940,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>65.91200000000001</v>
+        <v>67</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>65.4975</v>
+        <v>65.91200000000001</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
@@ -50780,40 +50982,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>64.7</v>
+        <v>65.4975</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>64.67400000000001</v>
+        <v>64.7</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -50822,61 +51024,61 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>62.22</v>
+        <v>64.67400000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>60.05</v>
+        <v>62.22</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>56.54</v>
+        <v>60.05</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -50885,19 +51087,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>55.55</v>
+        <v>56.54</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -50906,49 +51108,49 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>53.3</v>
+        <v>55.55</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>Roma Nomentana</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>51.866</v>
+        <v>53.3</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -50960,7 +51162,7 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>51.807</v>
+        <v>51.866</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -50969,19 +51171,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>51.3</v>
+        <v>51.807</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -50990,19 +51192,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -51011,61 +51213,61 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>50.19</v>
+        <v>50.6</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>47.9</v>
+        <v>50.19</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>47.47</v>
+        <v>47.9</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -51074,28 +51276,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>45.469</v>
+        <v>47.47</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -51104,31 +51306,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>44.036</v>
+        <v>45.469</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>43.65</v>
+        <v>44.036</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -51137,61 +51339,61 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>41.875</v>
+        <v>43.65</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>41.758</v>
+        <v>41.875</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>40.31</v>
+        <v>41.758</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -51200,22 +51402,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>40.287</v>
+        <v>40.31</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -52511,7 +52713,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
@@ -52521,7 +52723,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10322.3015</v>
+        <v>10378.3715</v>
       </c>
     </row>
     <row r="4">
@@ -52541,7 +52743,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -52777,28 +52979,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Viterbo</t>
+          <t>Ferrara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>284.99</v>
+        <v>288.336</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Viterbo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -52807,34 +53009,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>274.185</v>
+        <v>284.99</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ferrara</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>232.266</v>
+        <v>274.185</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -53909,13 +54111,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>4010.8185</v>
+        <v>4066.8885</v>
       </c>
     </row>
     <row r="3">
